--- a/research/traditional_assets/database/data/oman/oman_utility_general.xlsx
+++ b/research/traditional_assets/database/data/oman/oman_utility_general.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0798815958613017</v>
+        <v>0.07980002346750974</v>
       </c>
       <c r="C2">
-        <v>179.752112703501</v>
+        <v>178.2214955917308</v>
       </c>
       <c r="D2">
-        <v>172.492112703501</v>
+        <v>172.6714955917308</v>
       </c>
       <c r="E2">
-        <v>-37.2</v>
+        <v>-35.49</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="G2">
         <v>7.26</v>
@@ -1445,28 +1445,28 @@
         <v>22.62</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.08601299999999999</v>
       </c>
       <c r="N2">
-        <v>22.62</v>
+        <v>22.533987</v>
       </c>
       <c r="O2">
-        <v>3.393</v>
+        <v>3.38009805</v>
       </c>
       <c r="P2">
-        <v>19.227</v>
+        <v>19.15388895</v>
       </c>
       <c r="Q2">
-        <v>19.232</v>
+        <v>19.15888895</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0798815958613017</v>
+        <v>0.08017421562374721</v>
       </c>
       <c r="T2">
-        <v>0.4441974458563938</v>
+        <v>0.4480112623107163</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>262.9835024938091</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07980002346750974</v>
+        <v>0.07971845107371779</v>
       </c>
       <c r="C3">
-        <v>178.2214955917308</v>
+        <v>176.6912519662447</v>
       </c>
       <c r="D3">
-        <v>172.6714955917308</v>
+        <v>172.8512519662447</v>
       </c>
       <c r="E3">
-        <v>-35.49</v>
+        <v>-33.78</v>
       </c>
       <c r="F3">
-        <v>1.71</v>
+        <v>3.42</v>
       </c>
       <c r="G3">
         <v>7.26</v>
@@ -1527,28 +1527,28 @@
         <v>22.62</v>
       </c>
       <c r="M3">
-        <v>0.08601299999999999</v>
+        <v>0.172026</v>
       </c>
       <c r="N3">
-        <v>22.533987</v>
+        <v>22.447974</v>
       </c>
       <c r="O3">
-        <v>3.38009805</v>
+        <v>3.3671961</v>
       </c>
       <c r="P3">
-        <v>19.15388895</v>
+        <v>19.0807779</v>
       </c>
       <c r="Q3">
-        <v>19.15888895</v>
+        <v>19.0857779</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08017421562374721</v>
+        <v>0.08047280721807938</v>
       </c>
       <c r="T3">
-        <v>0.4480112623107163</v>
+        <v>0.4519029117539027</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>262.9835024938091</v>
+        <v>131.4917512469046</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07971845107371779</v>
+        <v>0.07963687867992583</v>
       </c>
       <c r="C4">
-        <v>176.6912519662447</v>
+        <v>175.1613829946907</v>
       </c>
       <c r="D4">
-        <v>172.8512519662447</v>
+        <v>173.0313829946907</v>
       </c>
       <c r="E4">
-        <v>-33.78</v>
+        <v>-32.07</v>
       </c>
       <c r="F4">
-        <v>3.42</v>
+        <v>5.13</v>
       </c>
       <c r="G4">
         <v>7.26</v>
@@ -1609,28 +1609,28 @@
         <v>22.62</v>
       </c>
       <c r="M4">
-        <v>0.172026</v>
+        <v>0.258039</v>
       </c>
       <c r="N4">
-        <v>22.447974</v>
+        <v>22.361961</v>
       </c>
       <c r="O4">
-        <v>3.3671961</v>
+        <v>3.35429415</v>
       </c>
       <c r="P4">
-        <v>19.0807779</v>
+        <v>19.00766685</v>
       </c>
       <c r="Q4">
-        <v>19.0857779</v>
+        <v>19.01266685</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08047280721807938</v>
+        <v>0.08077755534012973</v>
       </c>
       <c r="T4">
-        <v>0.4519029117539027</v>
+        <v>0.4558748013917938</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>131.4917512469046</v>
+        <v>87.66116749793638</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07963687867992583</v>
+        <v>0.07955530628613387</v>
       </c>
       <c r="C5">
-        <v>175.1613829946907</v>
+        <v>173.6318898495892</v>
       </c>
       <c r="D5">
-        <v>173.0313829946907</v>
+        <v>173.2118898495892</v>
       </c>
       <c r="E5">
-        <v>-32.07</v>
+        <v>-30.36</v>
       </c>
       <c r="F5">
-        <v>5.13</v>
+        <v>6.84</v>
       </c>
       <c r="G5">
         <v>7.26</v>
@@ -1691,28 +1691,28 @@
         <v>22.62</v>
       </c>
       <c r="M5">
-        <v>0.258039</v>
+        <v>0.344052</v>
       </c>
       <c r="N5">
-        <v>22.361961</v>
+        <v>22.275948</v>
       </c>
       <c r="O5">
-        <v>3.35429415</v>
+        <v>3.3413922</v>
       </c>
       <c r="P5">
-        <v>19.00766685</v>
+        <v>18.9345558</v>
       </c>
       <c r="Q5">
-        <v>19.01266685</v>
+        <v>18.9395558</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08077755534012973</v>
+        <v>0.08108865238138946</v>
       </c>
       <c r="T5">
-        <v>0.4558748013917938</v>
+        <v>0.4599294387304744</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>87.66116749793638</v>
+        <v>65.74587562345228</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07955530628613387</v>
+        <v>0.07947373389234193</v>
       </c>
       <c r="C6">
-        <v>173.6318898495892</v>
+        <v>172.1027737083581</v>
       </c>
       <c r="D6">
-        <v>173.2118898495892</v>
+        <v>173.3927737083581</v>
       </c>
       <c r="E6">
-        <v>-30.36</v>
+        <v>-28.65</v>
       </c>
       <c r="F6">
-        <v>6.84</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G6">
         <v>7.26</v>
@@ -1773,28 +1773,28 @@
         <v>22.62</v>
       </c>
       <c r="M6">
-        <v>0.344052</v>
+        <v>0.430065</v>
       </c>
       <c r="N6">
-        <v>22.275948</v>
+        <v>22.189935</v>
       </c>
       <c r="O6">
-        <v>3.3413922</v>
+        <v>3.32849025</v>
       </c>
       <c r="P6">
-        <v>18.9345558</v>
+        <v>18.86144475</v>
       </c>
       <c r="Q6">
-        <v>18.9395558</v>
+        <v>18.86644475</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08108865238138946</v>
+        <v>0.08140629883404414</v>
       </c>
       <c r="T6">
-        <v>0.4599294387304744</v>
+        <v>0.4640694368552324</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>65.74587562345228</v>
+        <v>52.59670049876181</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07947373389234193</v>
+        <v>0.07939216149854998</v>
       </c>
       <c r="C7">
-        <v>172.1027737083581</v>
+        <v>170.5740357533392</v>
       </c>
       <c r="D7">
-        <v>173.3927737083581</v>
+        <v>173.5740357533392</v>
       </c>
       <c r="E7">
-        <v>-28.65</v>
+        <v>-26.94</v>
       </c>
       <c r="F7">
-        <v>8.550000000000001</v>
+        <v>10.26</v>
       </c>
       <c r="G7">
         <v>7.26</v>
@@ -1855,28 +1855,28 @@
         <v>22.62</v>
       </c>
       <c r="M7">
-        <v>0.430065</v>
+        <v>0.516078</v>
       </c>
       <c r="N7">
-        <v>22.189935</v>
+        <v>22.103922</v>
       </c>
       <c r="O7">
-        <v>3.32849025</v>
+        <v>3.3155883</v>
       </c>
       <c r="P7">
-        <v>18.86144475</v>
+        <v>18.7883337</v>
       </c>
       <c r="Q7">
-        <v>18.86644475</v>
+        <v>18.7933337</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08140629883404414</v>
+        <v>0.08173070372186168</v>
       </c>
       <c r="T7">
-        <v>0.4640694368552324</v>
+        <v>0.4682975200464747</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>52.59670049876181</v>
+        <v>43.83058374896818</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07939216149854997</v>
+        <v>0.07931058910475804</v>
       </c>
       <c r="C8">
-        <v>170.5740357533392</v>
+        <v>169.045677171823</v>
       </c>
       <c r="D8">
-        <v>173.5740357533392</v>
+        <v>173.755677171823</v>
       </c>
       <c r="E8">
-        <v>-26.94</v>
+        <v>-25.23</v>
       </c>
       <c r="F8">
-        <v>10.26</v>
+        <v>11.97</v>
       </c>
       <c r="G8">
         <v>7.26</v>
@@ -1937,28 +1937,28 @@
         <v>22.62</v>
       </c>
       <c r="M8">
-        <v>0.5160779999999999</v>
+        <v>0.6020909999999999</v>
       </c>
       <c r="N8">
-        <v>22.103922</v>
+        <v>22.017909</v>
       </c>
       <c r="O8">
-        <v>3.3155883</v>
+        <v>3.30268635</v>
       </c>
       <c r="P8">
-        <v>18.7883337</v>
+        <v>18.71522265</v>
       </c>
       <c r="Q8">
-        <v>18.7933337</v>
+        <v>18.72022265</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08173070372186168</v>
+        <v>0.0820620850588796</v>
       </c>
       <c r="T8">
-        <v>0.4682975200464747</v>
+        <v>0.4726165297579587</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>43.83058374896819</v>
+        <v>37.56907178482987</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07931058910475804</v>
+        <v>0.07922901671096608</v>
       </c>
       <c r="C9">
-        <v>169.045677171823</v>
+        <v>167.5176991560754</v>
       </c>
       <c r="D9">
-        <v>173.755677171823</v>
+        <v>173.9376991560754</v>
       </c>
       <c r="E9">
-        <v>-25.23</v>
+        <v>-23.52</v>
       </c>
       <c r="F9">
-        <v>11.97</v>
+        <v>13.68</v>
       </c>
       <c r="G9">
         <v>7.26</v>
@@ -2019,28 +2019,28 @@
         <v>22.62</v>
       </c>
       <c r="M9">
-        <v>0.602091</v>
+        <v>0.6881039999999999</v>
       </c>
       <c r="N9">
-        <v>22.017909</v>
+        <v>21.931896</v>
       </c>
       <c r="O9">
-        <v>3.30268635</v>
+        <v>3.2897844</v>
       </c>
       <c r="P9">
-        <v>18.71522265</v>
+        <v>18.6421116</v>
       </c>
       <c r="Q9">
-        <v>18.72022265</v>
+        <v>18.6471116</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0820620850588796</v>
+        <v>0.0824006703380066</v>
       </c>
       <c r="T9">
-        <v>0.4726165297579587</v>
+        <v>0.4770294309849099</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>37.56907178482987</v>
+        <v>32.87293781172614</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07922901671096608</v>
+        <v>0.07914744431717413</v>
       </c>
       <c r="C10">
-        <v>167.5176991560754</v>
+        <v>165.9901029033634</v>
       </c>
       <c r="D10">
-        <v>173.9376991560754</v>
+        <v>174.1201029033634</v>
       </c>
       <c r="E10">
-        <v>-23.52</v>
+        <v>-21.81</v>
       </c>
       <c r="F10">
-        <v>13.68</v>
+        <v>15.39</v>
       </c>
       <c r="G10">
         <v>7.26</v>
@@ -2101,28 +2101,28 @@
         <v>22.62</v>
       </c>
       <c r="M10">
-        <v>0.6881039999999999</v>
+        <v>0.7741169999999999</v>
       </c>
       <c r="N10">
-        <v>21.931896</v>
+        <v>21.845883</v>
       </c>
       <c r="O10">
-        <v>3.2897844</v>
+        <v>3.27688245</v>
       </c>
       <c r="P10">
-        <v>18.6421116</v>
+        <v>18.56900055</v>
       </c>
       <c r="Q10">
-        <v>18.6471116</v>
+        <v>18.57400055</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0824006703380066</v>
+        <v>0.08274669705183969</v>
       </c>
       <c r="T10">
-        <v>0.4770294309849099</v>
+        <v>0.4815393190520136</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.87293781172614</v>
+        <v>29.22038916597879</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07914744431717413</v>
+        <v>0.07906587192338217</v>
       </c>
       <c r="C11">
-        <v>165.9901029033634</v>
+        <v>164.4628896159815</v>
       </c>
       <c r="D11">
-        <v>174.1201029033634</v>
+        <v>174.3028896159815</v>
       </c>
       <c r="E11">
-        <v>-21.81</v>
+        <v>-20.1</v>
       </c>
       <c r="F11">
-        <v>15.39</v>
+        <v>17.1</v>
       </c>
       <c r="G11">
         <v>7.26</v>
@@ -2183,28 +2183,28 @@
         <v>22.62</v>
       </c>
       <c r="M11">
-        <v>0.7741169999999999</v>
+        <v>0.8601299999999998</v>
       </c>
       <c r="N11">
-        <v>21.845883</v>
+        <v>21.75987</v>
       </c>
       <c r="O11">
-        <v>3.27688245</v>
+        <v>3.2639805</v>
       </c>
       <c r="P11">
-        <v>18.56900055</v>
+        <v>18.4958895</v>
       </c>
       <c r="Q11">
-        <v>18.57400055</v>
+        <v>18.5008895</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08274669705183969</v>
+        <v>0.08310041324820241</v>
       </c>
       <c r="T11">
-        <v>0.4815393190520136</v>
+        <v>0.4861494268539421</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>29.22038916597879</v>
+        <v>26.29835024938091</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07906587192338217</v>
+        <v>0.07898429952959023</v>
       </c>
       <c r="C12">
-        <v>164.4628896159815</v>
+        <v>162.9360605012778</v>
       </c>
       <c r="D12">
-        <v>174.3028896159815</v>
+        <v>174.4860605012778</v>
       </c>
       <c r="E12">
-        <v>-20.1</v>
+        <v>-18.39</v>
       </c>
       <c r="F12">
-        <v>17.1</v>
+        <v>18.81</v>
       </c>
       <c r="G12">
         <v>7.26</v>
@@ -2265,28 +2265,28 @@
         <v>22.62</v>
       </c>
       <c r="M12">
-        <v>0.8601300000000001</v>
+        <v>0.9461429999999998</v>
       </c>
       <c r="N12">
-        <v>21.75987</v>
+        <v>21.673857</v>
       </c>
       <c r="O12">
-        <v>3.2639805</v>
+        <v>3.25107855</v>
       </c>
       <c r="P12">
-        <v>18.4958895</v>
+        <v>18.42277845</v>
       </c>
       <c r="Q12">
-        <v>18.5008895</v>
+        <v>18.42777845</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08310041324820241</v>
+        <v>0.08346207812313508</v>
       </c>
       <c r="T12">
-        <v>0.4861494268539421</v>
+        <v>0.4908631325840037</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>26.29835024938091</v>
+        <v>23.90759113580083</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07898429952959023</v>
+        <v>0.07890272713579828</v>
       </c>
       <c r="C13">
-        <v>162.9360605012778</v>
+        <v>161.4096167716812</v>
       </c>
       <c r="D13">
-        <v>174.4860605012778</v>
+        <v>174.6696167716812</v>
       </c>
       <c r="E13">
-        <v>-18.39</v>
+        <v>-16.68</v>
       </c>
       <c r="F13">
-        <v>18.81</v>
+        <v>20.52</v>
       </c>
       <c r="G13">
         <v>7.26</v>
@@ -2347,28 +2347,28 @@
         <v>22.62</v>
       </c>
       <c r="M13">
-        <v>0.9461429999999998</v>
+        <v>1.032156</v>
       </c>
       <c r="N13">
-        <v>21.673857</v>
+        <v>21.587844</v>
       </c>
       <c r="O13">
-        <v>3.25107855</v>
+        <v>3.2381766</v>
       </c>
       <c r="P13">
-        <v>18.42277845</v>
+        <v>18.3496674</v>
       </c>
       <c r="Q13">
-        <v>18.42777845</v>
+        <v>18.3546674</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08346207812313508</v>
+        <v>0.08383196265431622</v>
       </c>
       <c r="T13">
-        <v>0.4908631325840037</v>
+        <v>0.4956839679897485</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.90759113580083</v>
+        <v>21.91529187448409</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07890272713579828</v>
+        <v>0.07882115474200631</v>
       </c>
       <c r="C14">
-        <v>161.4096167716812</v>
+        <v>159.8835596447276</v>
       </c>
       <c r="D14">
-        <v>174.6696167716812</v>
+        <v>174.8535596447276</v>
       </c>
       <c r="E14">
-        <v>-16.68</v>
+        <v>-14.97</v>
       </c>
       <c r="F14">
-        <v>20.52</v>
+        <v>22.23</v>
       </c>
       <c r="G14">
         <v>7.26</v>
@@ -2429,28 +2429,28 @@
         <v>22.62</v>
       </c>
       <c r="M14">
-        <v>1.032156</v>
+        <v>1.118169</v>
       </c>
       <c r="N14">
-        <v>21.587844</v>
+        <v>21.501831</v>
       </c>
       <c r="O14">
-        <v>3.2381766</v>
+        <v>3.22527465</v>
       </c>
       <c r="P14">
-        <v>18.3496674</v>
+        <v>18.27655635</v>
       </c>
       <c r="Q14">
-        <v>18.3546674</v>
+        <v>18.28155635</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08383196265431622</v>
+        <v>0.08421035027816817</v>
       </c>
       <c r="T14">
-        <v>0.4956839679897485</v>
+        <v>0.5006156271979242</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.91529187448409</v>
+        <v>20.22950019183147</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07882115474200631</v>
+        <v>0.07873958234821436</v>
       </c>
       <c r="C15">
-        <v>159.8835596447276</v>
+        <v>158.3578903430869</v>
       </c>
       <c r="D15">
-        <v>174.8535596447276</v>
+        <v>175.0378903430869</v>
       </c>
       <c r="E15">
-        <v>-14.97</v>
+        <v>-13.26</v>
       </c>
       <c r="F15">
-        <v>22.23</v>
+        <v>23.94</v>
       </c>
       <c r="G15">
         <v>7.26</v>
@@ -2511,28 +2511,28 @@
         <v>22.62</v>
       </c>
       <c r="M15">
-        <v>1.118169</v>
+        <v>1.204182</v>
       </c>
       <c r="N15">
-        <v>21.501831</v>
+        <v>21.415818</v>
       </c>
       <c r="O15">
-        <v>3.22527465</v>
+        <v>3.2123727</v>
       </c>
       <c r="P15">
-        <v>18.27655635</v>
+        <v>18.2034453</v>
       </c>
       <c r="Q15">
-        <v>18.28155635</v>
+        <v>18.2084453</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08421035027816817</v>
+        <v>0.08459753761420274</v>
       </c>
       <c r="T15">
-        <v>0.5006156271979242</v>
+        <v>0.5056619761551273</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>20.22950019183147</v>
+        <v>18.78453589241493</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07873958234821436</v>
+        <v>0.0786580099544224</v>
       </c>
       <c r="C16">
-        <v>158.3578903430869</v>
+        <v>156.8326100945904</v>
       </c>
       <c r="D16">
-        <v>175.0378903430869</v>
+        <v>175.2226100945904</v>
       </c>
       <c r="E16">
-        <v>-13.26</v>
+        <v>-11.55</v>
       </c>
       <c r="F16">
-        <v>23.94</v>
+        <v>25.65</v>
       </c>
       <c r="G16">
         <v>7.26</v>
@@ -2593,28 +2593,28 @@
         <v>22.62</v>
       </c>
       <c r="M16">
-        <v>1.204182</v>
+        <v>1.290195</v>
       </c>
       <c r="N16">
-        <v>21.415818</v>
+        <v>21.329805</v>
       </c>
       <c r="O16">
-        <v>3.2123727</v>
+        <v>3.19947075</v>
       </c>
       <c r="P16">
-        <v>18.2034453</v>
+        <v>18.13033425</v>
       </c>
       <c r="Q16">
-        <v>18.2084453</v>
+        <v>18.13533425</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08459753761420274</v>
+        <v>0.08499383524049695</v>
       </c>
       <c r="T16">
-        <v>0.5056619761551273</v>
+        <v>0.5108270627348528</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.78453589241493</v>
+        <v>17.53223349958727</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0786580099544224</v>
+        <v>0.07857643756063046</v>
       </c>
       <c r="C17">
-        <v>156.8326100945904</v>
+        <v>155.3077201322577</v>
       </c>
       <c r="D17">
-        <v>175.2226100945904</v>
+        <v>175.4077201322577</v>
       </c>
       <c r="E17">
-        <v>-11.55</v>
+        <v>-9.840000000000003</v>
       </c>
       <c r="F17">
-        <v>25.65</v>
+        <v>27.36</v>
       </c>
       <c r="G17">
         <v>7.26</v>
@@ -2675,28 +2675,28 @@
         <v>22.62</v>
       </c>
       <c r="M17">
-        <v>1.290195</v>
+        <v>1.376208</v>
       </c>
       <c r="N17">
-        <v>21.329805</v>
+        <v>21.243792</v>
       </c>
       <c r="O17">
-        <v>3.19947075</v>
+        <v>3.1865688</v>
       </c>
       <c r="P17">
-        <v>18.13033425</v>
+        <v>18.0572232</v>
       </c>
       <c r="Q17">
-        <v>18.13533425</v>
+        <v>18.0622232</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08499383524049695</v>
+        <v>0.08539956852456007</v>
       </c>
       <c r="T17">
-        <v>0.5108270627348528</v>
+        <v>0.5161151275664766</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.53223349958727</v>
+        <v>16.43646890586307</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07857643756063046</v>
+        <v>0.07849486516683851</v>
       </c>
       <c r="C18">
-        <v>155.3077201322577</v>
+        <v>153.7832216943245</v>
       </c>
       <c r="D18">
-        <v>175.4077201322577</v>
+        <v>175.5932216943245</v>
       </c>
       <c r="E18">
-        <v>-9.840000000000003</v>
+        <v>-8.129999999999999</v>
       </c>
       <c r="F18">
-        <v>27.36</v>
+        <v>29.07</v>
       </c>
       <c r="G18">
         <v>7.26</v>
@@ -2757,28 +2757,28 @@
         <v>22.62</v>
       </c>
       <c r="M18">
-        <v>1.376208</v>
+        <v>1.462221</v>
       </c>
       <c r="N18">
-        <v>21.243792</v>
+        <v>21.157779</v>
       </c>
       <c r="O18">
-        <v>3.1865688</v>
+        <v>3.17366685</v>
       </c>
       <c r="P18">
-        <v>18.0572232</v>
+        <v>17.98411215</v>
       </c>
       <c r="Q18">
-        <v>18.0622232</v>
+        <v>17.98911215</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08539956852456007</v>
+        <v>0.08581507851426326</v>
       </c>
       <c r="T18">
-        <v>0.5161151275664766</v>
+        <v>0.5215306156470551</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.43646890586307</v>
+        <v>15.46961779375347</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07849486516683851</v>
+        <v>0.07841329277304655</v>
       </c>
       <c r="C19">
-        <v>153.7832216943245</v>
+        <v>152.2591160242699</v>
       </c>
       <c r="D19">
-        <v>175.5932216943245</v>
+        <v>175.7791160242699</v>
       </c>
       <c r="E19">
-        <v>-8.129999999999999</v>
+        <v>-6.419999999999998</v>
       </c>
       <c r="F19">
-        <v>29.07</v>
+        <v>30.78</v>
       </c>
       <c r="G19">
         <v>7.26</v>
@@ -2839,28 +2839,28 @@
         <v>22.62</v>
       </c>
       <c r="M19">
-        <v>1.462221</v>
+        <v>1.548234</v>
       </c>
       <c r="N19">
-        <v>21.157779</v>
+        <v>21.071766</v>
       </c>
       <c r="O19">
-        <v>3.17366685</v>
+        <v>3.1607649</v>
       </c>
       <c r="P19">
-        <v>17.98411215</v>
+        <v>17.9110011</v>
       </c>
       <c r="Q19">
-        <v>17.98911215</v>
+        <v>17.9160011</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08581507851426326</v>
+        <v>0.0862407228939592</v>
       </c>
       <c r="T19">
-        <v>0.5215306156470551</v>
+        <v>0.5270781888027697</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.46961779375347</v>
+        <v>14.61019458298939</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07841329277304654</v>
+        <v>0.07833172037925461</v>
       </c>
       <c r="C20">
-        <v>152.2591160242699</v>
+        <v>150.7354043708441</v>
       </c>
       <c r="D20">
-        <v>175.7791160242699</v>
+        <v>175.9654043708441</v>
       </c>
       <c r="E20">
-        <v>-6.420000000000005</v>
+        <v>-4.710000000000001</v>
       </c>
       <c r="F20">
-        <v>30.78</v>
+        <v>32.49</v>
       </c>
       <c r="G20">
         <v>7.26</v>
@@ -2921,28 +2921,28 @@
         <v>22.62</v>
       </c>
       <c r="M20">
-        <v>1.548234</v>
+        <v>1.634247</v>
       </c>
       <c r="N20">
-        <v>21.071766</v>
+        <v>20.985753</v>
       </c>
       <c r="O20">
-        <v>3.1607649</v>
+        <v>3.14786295</v>
       </c>
       <c r="P20">
-        <v>17.9110011</v>
+        <v>17.83789005</v>
       </c>
       <c r="Q20">
-        <v>17.9160011</v>
+        <v>17.84289005</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0862407228939592</v>
+        <v>0.08667687701142543</v>
       </c>
       <c r="T20">
-        <v>0.5270781888027697</v>
+        <v>0.5327627390734401</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.61019458298939</v>
+        <v>13.84123697335837</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07833172037925461</v>
+        <v>0.07825014798546265</v>
       </c>
       <c r="C21">
-        <v>150.7354043708441</v>
+        <v>149.2120879880969</v>
       </c>
       <c r="D21">
-        <v>175.9654043708441</v>
+        <v>176.1520879880969</v>
       </c>
       <c r="E21">
-        <v>-4.710000000000001</v>
+        <v>-3</v>
       </c>
       <c r="F21">
-        <v>32.49</v>
+        <v>34.2</v>
       </c>
       <c r="G21">
         <v>7.26</v>
@@ -3003,28 +3003,28 @@
         <v>22.62</v>
       </c>
       <c r="M21">
-        <v>1.634247</v>
+        <v>1.72026</v>
       </c>
       <c r="N21">
-        <v>20.985753</v>
+        <v>20.89974</v>
       </c>
       <c r="O21">
-        <v>3.14786295</v>
+        <v>3.134961</v>
       </c>
       <c r="P21">
-        <v>17.83789005</v>
+        <v>17.764779</v>
       </c>
       <c r="Q21">
-        <v>17.84289005</v>
+        <v>17.769779</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08667687701142543</v>
+        <v>0.0871239349818283</v>
       </c>
       <c r="T21">
-        <v>0.5327627390734401</v>
+        <v>0.5385894031008774</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>13.84123697335837</v>
+        <v>13.14917512469045</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07825014798546265</v>
+        <v>0.0784363255916707</v>
       </c>
       <c r="C22">
-        <v>149.2120879880969</v>
+        <v>147.076586949566</v>
       </c>
       <c r="D22">
-        <v>176.1520879880969</v>
+        <v>175.726586949566</v>
       </c>
       <c r="E22">
-        <v>-3</v>
+        <v>-1.289999999999999</v>
       </c>
       <c r="F22">
-        <v>34.2</v>
+        <v>35.91</v>
       </c>
       <c r="G22">
         <v>7.26</v>
@@ -3085,45 +3085,45 @@
         <v>22.62</v>
       </c>
       <c r="M22">
-        <v>1.72026</v>
+        <v>1.860138</v>
       </c>
       <c r="N22">
-        <v>20.89974</v>
+        <v>20.759862</v>
       </c>
       <c r="O22">
-        <v>3.134961</v>
+        <v>3.1139793</v>
       </c>
       <c r="P22">
-        <v>17.764779</v>
+        <v>17.6458827</v>
       </c>
       <c r="Q22">
-        <v>17.769779</v>
+        <v>17.6508827</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0871239349818283</v>
+        <v>0.08758231087553253</v>
       </c>
       <c r="T22">
-        <v>0.5385894031008774</v>
+        <v>0.5445635776100221</v>
       </c>
       <c r="U22">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V22">
         <v>0.15</v>
       </c>
       <c r="W22">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y22">
-        <v>13.14917512469045</v>
+        <v>12.16038810023772</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07843632559167069</v>
+        <v>0.07836750319787875</v>
       </c>
       <c r="C23">
-        <v>147.0765869495661</v>
+        <v>145.5236379116052</v>
       </c>
       <c r="D23">
-        <v>175.7265869495661</v>
+        <v>175.8836379116052</v>
       </c>
       <c r="E23">
-        <v>-1.290000000000006</v>
+        <v>0.4199999999999946</v>
       </c>
       <c r="F23">
-        <v>35.91</v>
+        <v>37.62</v>
       </c>
       <c r="G23">
         <v>7.26</v>
@@ -3167,28 +3167,28 @@
         <v>22.62</v>
       </c>
       <c r="M23">
-        <v>1.860138</v>
+        <v>1.948716</v>
       </c>
       <c r="N23">
-        <v>20.759862</v>
+        <v>20.671284</v>
       </c>
       <c r="O23">
-        <v>3.1139793</v>
+        <v>3.1006926</v>
       </c>
       <c r="P23">
-        <v>17.6458827</v>
+        <v>17.5705914</v>
       </c>
       <c r="Q23">
-        <v>17.6508827</v>
+        <v>17.5755914</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08758231087553252</v>
+        <v>0.08805243999728044</v>
       </c>
       <c r="T23">
-        <v>0.5445635776100219</v>
+        <v>0.5506909360809394</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>12.16038810023773</v>
+        <v>11.60764318659056</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07836750319787875</v>
+        <v>0.07829868080408678</v>
       </c>
       <c r="C24">
-        <v>145.5236379116052</v>
+        <v>143.9709698449932</v>
       </c>
       <c r="D24">
-        <v>175.8836379116052</v>
+        <v>176.0409698449933</v>
       </c>
       <c r="E24">
-        <v>0.4199999999999946</v>
+        <v>2.129999999999995</v>
       </c>
       <c r="F24">
-        <v>37.62</v>
+        <v>39.33</v>
       </c>
       <c r="G24">
         <v>7.26</v>
@@ -3249,28 +3249,28 @@
         <v>22.62</v>
       </c>
       <c r="M24">
-        <v>1.948716</v>
+        <v>2.037294</v>
       </c>
       <c r="N24">
-        <v>20.671284</v>
+        <v>20.582706</v>
       </c>
       <c r="O24">
-        <v>3.1006926</v>
+        <v>3.0874059</v>
       </c>
       <c r="P24">
-        <v>17.5705914</v>
+        <v>17.4953001</v>
       </c>
       <c r="Q24">
-        <v>17.5755914</v>
+        <v>17.5003001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08805243999728044</v>
+        <v>0.08853478026504777</v>
       </c>
       <c r="T24">
-        <v>0.5506909360809394</v>
+        <v>0.5569774467199327</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.60764318659056</v>
+        <v>11.10296304804314</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07829868080408678</v>
+        <v>0.07822985841029484</v>
       </c>
       <c r="C25">
-        <v>143.9709698449932</v>
+        <v>142.4185835044112</v>
       </c>
       <c r="D25">
-        <v>176.0409698449933</v>
+        <v>176.1985835044112</v>
       </c>
       <c r="E25">
-        <v>2.129999999999995</v>
+        <v>3.840000000000003</v>
       </c>
       <c r="F25">
-        <v>39.33</v>
+        <v>41.04000000000001</v>
       </c>
       <c r="G25">
         <v>7.26</v>
@@ -3331,28 +3331,28 @@
         <v>22.62</v>
       </c>
       <c r="M25">
-        <v>2.037294</v>
+        <v>2.125872</v>
       </c>
       <c r="N25">
-        <v>20.582706</v>
+        <v>20.494128</v>
       </c>
       <c r="O25">
-        <v>3.0874059</v>
+        <v>3.0741192</v>
       </c>
       <c r="P25">
-        <v>17.4953001</v>
+        <v>17.4200088</v>
       </c>
       <c r="Q25">
-        <v>17.5003001</v>
+        <v>17.4250088</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08853478026504777</v>
+        <v>0.08902981369775637</v>
       </c>
       <c r="T25">
-        <v>0.5569774467199327</v>
+        <v>0.5634293918494258</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.10296304804314</v>
+        <v>10.64033958770801</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07822985841029484</v>
+        <v>0.07816103601650289</v>
       </c>
       <c r="C26">
-        <v>142.4185835044112</v>
+        <v>140.8664796472451</v>
       </c>
       <c r="D26">
-        <v>176.1985835044112</v>
+        <v>176.3564796472452</v>
       </c>
       <c r="E26">
-        <v>3.839999999999996</v>
+        <v>5.549999999999997</v>
       </c>
       <c r="F26">
-        <v>41.04</v>
+        <v>42.75</v>
       </c>
       <c r="G26">
         <v>7.26</v>
@@ -3413,28 +3413,28 @@
         <v>22.62</v>
       </c>
       <c r="M26">
-        <v>2.125872</v>
+        <v>2.21445</v>
       </c>
       <c r="N26">
-        <v>20.494128</v>
+        <v>20.40555</v>
       </c>
       <c r="O26">
-        <v>3.0741192</v>
+        <v>3.0608325</v>
       </c>
       <c r="P26">
-        <v>17.4200088</v>
+        <v>17.3447175</v>
       </c>
       <c r="Q26">
-        <v>17.4250088</v>
+        <v>17.3497175</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08902981369775637</v>
+        <v>0.08953804802200384</v>
       </c>
       <c r="T26">
-        <v>0.5634293918494258</v>
+        <v>0.5700533888490386</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.64033958770801</v>
+        <v>10.21472600419969</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07816103601650289</v>
+        <v>0.07809221362271093</v>
       </c>
       <c r="C27">
-        <v>140.8664796472451</v>
+        <v>139.3146590335984</v>
       </c>
       <c r="D27">
-        <v>176.3564796472452</v>
+        <v>176.5146590335985</v>
       </c>
       <c r="E27">
-        <v>5.549999999999997</v>
+        <v>7.259999999999998</v>
       </c>
       <c r="F27">
-        <v>42.75</v>
+        <v>44.46</v>
       </c>
       <c r="G27">
         <v>7.26</v>
@@ -3495,28 +3495,28 @@
         <v>22.62</v>
       </c>
       <c r="M27">
-        <v>2.21445</v>
+        <v>2.303028</v>
       </c>
       <c r="N27">
-        <v>20.40555</v>
+        <v>20.316972</v>
       </c>
       <c r="O27">
-        <v>3.0608325</v>
+        <v>3.0475458</v>
       </c>
       <c r="P27">
-        <v>17.3447175</v>
+        <v>17.2694262</v>
       </c>
       <c r="Q27">
-        <v>17.3497175</v>
+        <v>17.2744262</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08953804802200384</v>
+        <v>0.09006001840906883</v>
       </c>
       <c r="T27">
-        <v>0.5700533888490386</v>
+        <v>0.576856412794587</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.21472600419969</v>
+        <v>9.821851927115086</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07809221362271093</v>
+        <v>0.07841354122891898</v>
       </c>
       <c r="C28">
-        <v>139.3146590335984</v>
+        <v>136.8685492236313</v>
       </c>
       <c r="D28">
-        <v>176.5146590335985</v>
+        <v>175.7785492236313</v>
       </c>
       <c r="E28">
-        <v>7.259999999999998</v>
+        <v>8.969999999999999</v>
       </c>
       <c r="F28">
-        <v>44.46</v>
+        <v>46.17</v>
       </c>
       <c r="G28">
         <v>7.26</v>
@@ -3577,45 +3577,45 @@
         <v>22.62</v>
       </c>
       <c r="M28">
-        <v>2.303028</v>
+        <v>2.470095</v>
       </c>
       <c r="N28">
-        <v>20.316972</v>
+        <v>20.149905</v>
       </c>
       <c r="O28">
-        <v>3.0475458</v>
+        <v>3.02248575</v>
       </c>
       <c r="P28">
-        <v>17.2694262</v>
+        <v>17.12741925</v>
       </c>
       <c r="Q28">
-        <v>17.2744262</v>
+        <v>17.13241925</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09006001840906883</v>
+        <v>0.09059628935468353</v>
       </c>
       <c r="T28">
-        <v>0.576856412794587</v>
+        <v>0.5838458209578217</v>
       </c>
       <c r="U28">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V28">
         <v>0.15</v>
       </c>
       <c r="W28">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>9.821851927115086</v>
+        <v>9.157542523668118</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07841354122891898</v>
+        <v>0.07835916883512703</v>
       </c>
       <c r="C29">
-        <v>136.8685492236313</v>
+        <v>135.2826757746292</v>
       </c>
       <c r="D29">
-        <v>175.7785492236313</v>
+        <v>175.9026757746292</v>
       </c>
       <c r="E29">
-        <v>8.969999999999999</v>
+        <v>10.68</v>
       </c>
       <c r="F29">
-        <v>46.17</v>
+        <v>47.88</v>
       </c>
       <c r="G29">
         <v>7.26</v>
@@ -3659,28 +3659,28 @@
         <v>22.62</v>
       </c>
       <c r="M29">
-        <v>2.470095</v>
+        <v>2.56158</v>
       </c>
       <c r="N29">
-        <v>20.149905</v>
+        <v>20.05842</v>
       </c>
       <c r="O29">
-        <v>3.02248575</v>
+        <v>3.008763</v>
       </c>
       <c r="P29">
-        <v>17.12741925</v>
+        <v>17.049657</v>
       </c>
       <c r="Q29">
-        <v>17.13241925</v>
+        <v>17.054657</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09059628935468353</v>
+        <v>0.09114745671545421</v>
       </c>
       <c r="T29">
-        <v>0.5838458209578217</v>
+        <v>0.5910293793478129</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>9.157542523668118</v>
+        <v>8.830487433537114</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07835916883512703</v>
+        <v>0.07830479644133506</v>
       </c>
       <c r="C30">
-        <v>135.2826757746292</v>
+        <v>133.6969777541809</v>
       </c>
       <c r="D30">
-        <v>175.9026757746292</v>
+        <v>176.026977754181</v>
       </c>
       <c r="E30">
-        <v>10.68</v>
+        <v>12.39</v>
       </c>
       <c r="F30">
-        <v>47.88</v>
+        <v>49.59</v>
       </c>
       <c r="G30">
         <v>7.26</v>
@@ -3741,28 +3741,28 @@
         <v>22.62</v>
       </c>
       <c r="M30">
-        <v>2.56158</v>
+        <v>2.653065</v>
       </c>
       <c r="N30">
-        <v>20.05842</v>
+        <v>19.966935</v>
       </c>
       <c r="O30">
-        <v>3.008763</v>
+        <v>2.99504025</v>
       </c>
       <c r="P30">
-        <v>17.049657</v>
+        <v>16.97189475</v>
       </c>
       <c r="Q30">
-        <v>17.054657</v>
+        <v>16.97689475</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09114745671545421</v>
+        <v>0.09171414991737334</v>
       </c>
       <c r="T30">
-        <v>0.5910293793478129</v>
+        <v>0.5984152914952685</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.830487433537114</v>
+        <v>8.525987866863419</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07830479644133506</v>
+        <v>0.07825042404754312</v>
       </c>
       <c r="C31">
-        <v>133.6969777541809</v>
+        <v>132.1114555344502</v>
       </c>
       <c r="D31">
-        <v>176.026977754181</v>
+        <v>176.1514555344502</v>
       </c>
       <c r="E31">
-        <v>12.38999999999999</v>
+        <v>14.09999999999999</v>
       </c>
       <c r="F31">
-        <v>49.59</v>
+        <v>51.3</v>
       </c>
       <c r="G31">
         <v>7.26</v>
@@ -3823,28 +3823,28 @@
         <v>22.62</v>
       </c>
       <c r="M31">
-        <v>2.653065</v>
+        <v>2.74455</v>
       </c>
       <c r="N31">
-        <v>19.966935</v>
+        <v>19.87545</v>
       </c>
       <c r="O31">
-        <v>2.99504025</v>
+        <v>2.9813175</v>
       </c>
       <c r="P31">
-        <v>16.97189475</v>
+        <v>16.8941325</v>
       </c>
       <c r="Q31">
-        <v>16.97689475</v>
+        <v>16.8991325</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09171414991737334</v>
+        <v>0.09229703435363304</v>
       </c>
       <c r="T31">
-        <v>0.5984152914952685</v>
+        <v>0.6060122297040801</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.525987866863421</v>
+        <v>8.241788271301306</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07825042404754312</v>
+        <v>0.07819605165375115</v>
       </c>
       <c r="C32">
-        <v>132.1114555344502</v>
+        <v>130.5261094886542</v>
       </c>
       <c r="D32">
-        <v>176.1514555344502</v>
+        <v>176.2761094886542</v>
       </c>
       <c r="E32">
-        <v>14.09999999999999</v>
+        <v>15.81</v>
       </c>
       <c r="F32">
-        <v>51.3</v>
+        <v>53.01</v>
       </c>
       <c r="G32">
         <v>7.26</v>
@@ -3905,28 +3905,28 @@
         <v>22.62</v>
       </c>
       <c r="M32">
-        <v>2.74455</v>
+        <v>2.836035</v>
       </c>
       <c r="N32">
-        <v>19.87545</v>
+        <v>19.783965</v>
       </c>
       <c r="O32">
-        <v>2.9813175</v>
+        <v>2.96759475</v>
       </c>
       <c r="P32">
-        <v>16.8941325</v>
+        <v>16.81637025</v>
       </c>
       <c r="Q32">
-        <v>16.8991325</v>
+        <v>16.82137025</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09229703435363304</v>
+        <v>0.09289681399094372</v>
       </c>
       <c r="T32">
-        <v>0.6060122297040801</v>
+        <v>0.6138293690203934</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.241788271301306</v>
+        <v>7.975924133517394</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07819605165375115</v>
+        <v>0.0781416792599592</v>
       </c>
       <c r="C33">
-        <v>130.5261094886542</v>
+        <v>128.9409399910675</v>
       </c>
       <c r="D33">
-        <v>176.2761094886542</v>
+        <v>176.4009399910675</v>
       </c>
       <c r="E33">
-        <v>15.81</v>
+        <v>17.52</v>
       </c>
       <c r="F33">
-        <v>53.01</v>
+        <v>54.72</v>
       </c>
       <c r="G33">
         <v>7.26</v>
@@ -3987,28 +3987,28 @@
         <v>22.62</v>
       </c>
       <c r="M33">
-        <v>2.836035</v>
+        <v>2.92752</v>
       </c>
       <c r="N33">
-        <v>19.783965</v>
+        <v>19.69248</v>
       </c>
       <c r="O33">
-        <v>2.96759475</v>
+        <v>2.953872</v>
       </c>
       <c r="P33">
-        <v>16.81637025</v>
+        <v>16.738608</v>
       </c>
       <c r="Q33">
-        <v>16.82137025</v>
+        <v>16.743608</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09289681399094372</v>
+        <v>0.09351423420582236</v>
       </c>
       <c r="T33">
-        <v>0.6138293690203934</v>
+        <v>0.6218764241989512</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>7.975924133517394</v>
+        <v>7.726676504344975</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0781416792599592</v>
+        <v>0.07831170686616726</v>
       </c>
       <c r="C34">
-        <v>128.9409399910675</v>
+        <v>126.8411699290695</v>
       </c>
       <c r="D34">
-        <v>176.4009399910675</v>
+        <v>176.0111699290695</v>
       </c>
       <c r="E34">
-        <v>17.52</v>
+        <v>19.23</v>
       </c>
       <c r="F34">
-        <v>54.72</v>
+        <v>56.43</v>
       </c>
       <c r="G34">
         <v>7.26</v>
@@ -4069,45 +4069,45 @@
         <v>22.62</v>
       </c>
       <c r="M34">
-        <v>2.92752</v>
+        <v>3.064149</v>
       </c>
       <c r="N34">
-        <v>19.69248</v>
+        <v>19.555851</v>
       </c>
       <c r="O34">
-        <v>2.953872</v>
+        <v>2.93337765</v>
       </c>
       <c r="P34">
-        <v>16.738608</v>
+        <v>16.62247335</v>
       </c>
       <c r="Q34">
-        <v>16.743608</v>
+        <v>16.62747335</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09351423420582236</v>
+        <v>0.09415008487487651</v>
       </c>
       <c r="T34">
-        <v>0.6218764241989512</v>
+        <v>0.6301636899798542</v>
       </c>
       <c r="U34">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>7.726676504344975</v>
+        <v>7.38214753916993</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07831170686616726</v>
+        <v>0.0782641344723753</v>
       </c>
       <c r="C35">
-        <v>126.8411699290695</v>
+        <v>125.2400508912616</v>
       </c>
       <c r="D35">
-        <v>176.0111699290695</v>
+        <v>176.1200508912616</v>
       </c>
       <c r="E35">
-        <v>19.23</v>
+        <v>20.94</v>
       </c>
       <c r="F35">
-        <v>56.43</v>
+        <v>58.14000000000001</v>
       </c>
       <c r="G35">
         <v>7.26</v>
@@ -4151,28 +4151,28 @@
         <v>22.62</v>
       </c>
       <c r="M35">
-        <v>3.064149</v>
+        <v>3.157002</v>
       </c>
       <c r="N35">
-        <v>19.555851</v>
+        <v>19.462998</v>
       </c>
       <c r="O35">
-        <v>2.93337765</v>
+        <v>2.9194497</v>
       </c>
       <c r="P35">
-        <v>16.62247335</v>
+        <v>16.5435483</v>
       </c>
       <c r="Q35">
-        <v>16.62747335</v>
+        <v>16.5485483</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09415008487487651</v>
+        <v>0.09480520374602319</v>
       </c>
       <c r="T35">
-        <v>0.6301636899798542</v>
+        <v>0.638702085026845</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.38214753916993</v>
+        <v>7.165025552723754</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0782641344723753</v>
+        <v>0.07821656207858335</v>
       </c>
       <c r="C36">
-        <v>125.2400508912616</v>
+        <v>123.6390666449223</v>
       </c>
       <c r="D36">
-        <v>176.1200508912616</v>
+        <v>176.2290666449223</v>
       </c>
       <c r="E36">
-        <v>20.94</v>
+        <v>22.65000000000001</v>
       </c>
       <c r="F36">
-        <v>58.14000000000001</v>
+        <v>59.85000000000001</v>
       </c>
       <c r="G36">
         <v>7.26</v>
@@ -4233,28 +4233,28 @@
         <v>22.62</v>
       </c>
       <c r="M36">
-        <v>3.157002</v>
+        <v>3.249855000000001</v>
       </c>
       <c r="N36">
-        <v>19.462998</v>
+        <v>19.370145</v>
       </c>
       <c r="O36">
-        <v>2.9194497</v>
+        <v>2.90552175</v>
       </c>
       <c r="P36">
-        <v>16.5435483</v>
+        <v>16.46462325</v>
       </c>
       <c r="Q36">
-        <v>16.5485483</v>
+        <v>16.46962325</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09480520374602319</v>
+        <v>0.09548048012089748</v>
       </c>
       <c r="T36">
-        <v>0.638702085026845</v>
+        <v>0.6475031999214356</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>7.165025552723754</v>
+        <v>6.960310536931646</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07821656207858335</v>
+        <v>0.07816898968479141</v>
       </c>
       <c r="C37">
-        <v>123.6390666449223</v>
+        <v>122.0382174405084</v>
       </c>
       <c r="D37">
-        <v>176.2290666449223</v>
+        <v>176.3382174405084</v>
       </c>
       <c r="E37">
-        <v>22.65000000000001</v>
+        <v>24.36000000000001</v>
       </c>
       <c r="F37">
-        <v>59.85000000000001</v>
+        <v>61.56000000000001</v>
       </c>
       <c r="G37">
         <v>7.26</v>
@@ -4315,28 +4315,28 @@
         <v>22.62</v>
       </c>
       <c r="M37">
-        <v>3.249855000000001</v>
+        <v>3.342708</v>
       </c>
       <c r="N37">
-        <v>19.370145</v>
+        <v>19.277292</v>
       </c>
       <c r="O37">
-        <v>2.90552175</v>
+        <v>2.8915938</v>
       </c>
       <c r="P37">
-        <v>16.46462325</v>
+        <v>16.3856982</v>
       </c>
       <c r="Q37">
-        <v>16.46962325</v>
+        <v>16.3906982</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09548048012089748</v>
+        <v>0.09617685888248659</v>
       </c>
       <c r="T37">
-        <v>0.6475031999214356</v>
+        <v>0.6565793496564821</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.960310536931646</v>
+        <v>6.766968577572435</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0781689896847914</v>
+        <v>0.07812141729099945</v>
       </c>
       <c r="C38">
-        <v>122.0382174405084</v>
+        <v>120.4375035290979</v>
       </c>
       <c r="D38">
-        <v>176.3382174405085</v>
+        <v>176.4475035290979</v>
       </c>
       <c r="E38">
-        <v>24.35999999999999</v>
+        <v>26.06999999999999</v>
       </c>
       <c r="F38">
-        <v>61.56</v>
+        <v>63.27</v>
       </c>
       <c r="G38">
         <v>7.26</v>
@@ -4397,28 +4397,28 @@
         <v>22.62</v>
       </c>
       <c r="M38">
-        <v>3.342708</v>
+        <v>3.435561</v>
       </c>
       <c r="N38">
-        <v>19.277292</v>
+        <v>19.184439</v>
       </c>
       <c r="O38">
-        <v>2.8915938</v>
+        <v>2.87766585</v>
       </c>
       <c r="P38">
-        <v>16.3856982</v>
+        <v>16.30677315</v>
       </c>
       <c r="Q38">
-        <v>16.3906982</v>
+        <v>16.31177315</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09617685888248656</v>
+        <v>0.09689534490634832</v>
       </c>
       <c r="T38">
-        <v>0.656579349656482</v>
+        <v>0.665943631129149</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.766968577572436</v>
+        <v>6.584077534935343</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07812141729099945</v>
+        <v>0.07807384489720751</v>
       </c>
       <c r="C39">
-        <v>120.4375035290979</v>
+        <v>118.8369251623912</v>
       </c>
       <c r="D39">
-        <v>176.4475035290979</v>
+        <v>176.5569251623913</v>
       </c>
       <c r="E39">
-        <v>26.06999999999999</v>
+        <v>27.78</v>
       </c>
       <c r="F39">
-        <v>63.27</v>
+        <v>64.98</v>
       </c>
       <c r="G39">
         <v>7.26</v>
@@ -4479,28 +4479,28 @@
         <v>22.62</v>
       </c>
       <c r="M39">
-        <v>3.435561</v>
+        <v>3.528414</v>
       </c>
       <c r="N39">
-        <v>19.184439</v>
+        <v>19.091586</v>
       </c>
       <c r="O39">
-        <v>2.87766585</v>
+        <v>2.8637379</v>
       </c>
       <c r="P39">
-        <v>16.30677315</v>
+        <v>16.2278481</v>
       </c>
       <c r="Q39">
-        <v>16.31177315</v>
+        <v>16.2328481</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09689534490634832</v>
+        <v>0.09763700789872178</v>
       </c>
       <c r="T39">
-        <v>0.665943631129149</v>
+        <v>0.6756099861977086</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.584077534935343</v>
+        <v>6.41081233664757</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07807384489720751</v>
+        <v>0.07802627250341554</v>
       </c>
       <c r="C40">
-        <v>118.8369251623912</v>
+        <v>117.2364825927139</v>
       </c>
       <c r="D40">
-        <v>176.5569251623913</v>
+        <v>176.6664825927139</v>
       </c>
       <c r="E40">
-        <v>27.78</v>
+        <v>29.48999999999999</v>
       </c>
       <c r="F40">
-        <v>64.98</v>
+        <v>66.69</v>
       </c>
       <c r="G40">
         <v>7.26</v>
@@ -4561,28 +4561,28 @@
         <v>22.62</v>
       </c>
       <c r="M40">
-        <v>3.528414</v>
+        <v>3.621267</v>
       </c>
       <c r="N40">
-        <v>19.091586</v>
+        <v>18.998733</v>
       </c>
       <c r="O40">
-        <v>2.8637379</v>
+        <v>2.84980995</v>
       </c>
       <c r="P40">
-        <v>16.2278481</v>
+        <v>16.14892305</v>
       </c>
       <c r="Q40">
-        <v>16.2328481</v>
+        <v>16.15392305</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09763700789872178</v>
+        <v>0.09840298771051728</v>
       </c>
       <c r="T40">
-        <v>0.6756099861977086</v>
+        <v>0.685593270940647</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.41081233664757</v>
+        <v>6.246432533143786</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07802627250341554</v>
+        <v>0.07831870010962361</v>
       </c>
       <c r="C41">
-        <v>117.2364825927139</v>
+        <v>114.8551755437937</v>
       </c>
       <c r="D41">
-        <v>176.6664825927139</v>
+        <v>175.9951755437937</v>
       </c>
       <c r="E41">
-        <v>29.48999999999999</v>
+        <v>31.2</v>
       </c>
       <c r="F41">
-        <v>66.69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G41">
         <v>7.26</v>
@@ -4643,45 +4643,45 @@
         <v>22.62</v>
       </c>
       <c r="M41">
-        <v>3.621267</v>
+        <v>3.78252</v>
       </c>
       <c r="N41">
-        <v>18.998733</v>
+        <v>18.83748</v>
       </c>
       <c r="O41">
-        <v>2.84980995</v>
+        <v>2.825622</v>
       </c>
       <c r="P41">
-        <v>16.14892305</v>
+        <v>16.011858</v>
       </c>
       <c r="Q41">
-        <v>16.15392305</v>
+        <v>16.016858</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09840298771051728</v>
+        <v>0.09919450018270601</v>
       </c>
       <c r="T41">
-        <v>0.685593270940647</v>
+        <v>0.6959093318416837</v>
       </c>
       <c r="U41">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V41">
         <v>0.15</v>
       </c>
       <c r="W41">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>6.246432533143786</v>
+        <v>5.980140223977665</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07831870010962361</v>
+        <v>0.07827962771583165</v>
       </c>
       <c r="C42">
-        <v>114.8551755437937</v>
+        <v>113.234576056876</v>
       </c>
       <c r="D42">
-        <v>175.9951755437937</v>
+        <v>176.084576056876</v>
       </c>
       <c r="E42">
-        <v>31.2</v>
+        <v>32.91</v>
       </c>
       <c r="F42">
-        <v>68.40000000000001</v>
+        <v>70.11</v>
       </c>
       <c r="G42">
         <v>7.26</v>
@@ -4725,28 +4725,28 @@
         <v>22.62</v>
       </c>
       <c r="M42">
-        <v>3.78252</v>
+        <v>3.877083</v>
       </c>
       <c r="N42">
-        <v>18.83748</v>
+        <v>18.742917</v>
       </c>
       <c r="O42">
-        <v>2.825622</v>
+        <v>2.81143755</v>
       </c>
       <c r="P42">
-        <v>16.011858</v>
+        <v>15.93147945</v>
       </c>
       <c r="Q42">
-        <v>16.016858</v>
+        <v>15.93647945</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09919450018270601</v>
+        <v>0.1000128435861553</v>
       </c>
       <c r="T42">
-        <v>0.6959093318416837</v>
+        <v>0.7065750897224162</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.980140223977665</v>
+        <v>5.834283145344064</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07827962771583165</v>
+        <v>0.07824055532203969</v>
       </c>
       <c r="C43">
-        <v>113.234576056876</v>
+        <v>111.6140674419236</v>
       </c>
       <c r="D43">
-        <v>176.084576056876</v>
+        <v>176.1740674419236</v>
       </c>
       <c r="E43">
-        <v>32.91</v>
+        <v>34.62</v>
       </c>
       <c r="F43">
-        <v>70.11</v>
+        <v>71.82000000000001</v>
       </c>
       <c r="G43">
         <v>7.26</v>
@@ -4807,28 +4807,28 @@
         <v>22.62</v>
       </c>
       <c r="M43">
-        <v>3.877083</v>
+        <v>3.971646000000001</v>
       </c>
       <c r="N43">
-        <v>18.742917</v>
+        <v>18.648354</v>
       </c>
       <c r="O43">
-        <v>2.81143755</v>
+        <v>2.7972531</v>
       </c>
       <c r="P43">
-        <v>15.93147945</v>
+        <v>15.8511009</v>
       </c>
       <c r="Q43">
-        <v>15.93647945</v>
+        <v>15.8561009</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1000128435861553</v>
+        <v>0.1008594057276546</v>
       </c>
       <c r="T43">
-        <v>0.7065750897224162</v>
+        <v>0.7176086323576568</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.834283145344064</v>
+        <v>5.695371641883491</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07824055532203969</v>
+        <v>0.07820148292824773</v>
       </c>
       <c r="C44">
-        <v>111.6140674419236</v>
+        <v>109.9936498375583</v>
       </c>
       <c r="D44">
-        <v>176.1740674419236</v>
+        <v>176.2636498375583</v>
       </c>
       <c r="E44">
-        <v>34.61999999999999</v>
+        <v>36.33</v>
       </c>
       <c r="F44">
-        <v>71.81999999999999</v>
+        <v>73.53</v>
       </c>
       <c r="G44">
         <v>7.26</v>
@@ -4889,28 +4889,28 @@
         <v>22.62</v>
       </c>
       <c r="M44">
-        <v>3.971646</v>
+        <v>4.066209000000001</v>
       </c>
       <c r="N44">
-        <v>18.648354</v>
+        <v>18.553791</v>
       </c>
       <c r="O44">
-        <v>2.7972531</v>
+        <v>2.78306865</v>
       </c>
       <c r="P44">
-        <v>15.8511009</v>
+        <v>15.77072235</v>
       </c>
       <c r="Q44">
-        <v>15.8561009</v>
+        <v>15.77572235</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1008594057276546</v>
+        <v>0.1017356718039434</v>
       </c>
       <c r="T44">
-        <v>0.7176086323576567</v>
+        <v>0.7290293168397479</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.695371641883492</v>
+        <v>5.562921138583874</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07820148292824773</v>
+        <v>0.07816241053445579</v>
       </c>
       <c r="C45">
-        <v>109.9936498375583</v>
+        <v>108.3733233826841</v>
       </c>
       <c r="D45">
-        <v>176.2636498375583</v>
+        <v>176.3533233826842</v>
       </c>
       <c r="E45">
-        <v>36.33</v>
+        <v>38.03999999999999</v>
       </c>
       <c r="F45">
-        <v>73.53</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="G45">
         <v>7.26</v>
@@ -4971,28 +4971,28 @@
         <v>22.62</v>
       </c>
       <c r="M45">
-        <v>4.066209000000001</v>
+        <v>4.160772</v>
       </c>
       <c r="N45">
-        <v>18.553791</v>
+        <v>18.459228</v>
       </c>
       <c r="O45">
-        <v>2.78306865</v>
+        <v>2.7688842</v>
       </c>
       <c r="P45">
-        <v>15.77072235</v>
+        <v>15.6903438</v>
       </c>
       <c r="Q45">
-        <v>15.77572235</v>
+        <v>15.6953438</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1017356718039434</v>
+        <v>0.1026432330972425</v>
       </c>
       <c r="T45">
-        <v>0.7290293168397479</v>
+        <v>0.7408578829104853</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.562921138583874</v>
+        <v>5.43649111270697</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07816241053445579</v>
+        <v>0.07812333814066383</v>
       </c>
       <c r="C46">
-        <v>108.3733233826841</v>
+        <v>106.753088216488</v>
       </c>
       <c r="D46">
-        <v>176.3533233826842</v>
+        <v>176.443088216488</v>
       </c>
       <c r="E46">
-        <v>38.03999999999999</v>
+        <v>39.75</v>
       </c>
       <c r="F46">
-        <v>75.23999999999999</v>
+        <v>76.95</v>
       </c>
       <c r="G46">
         <v>7.26</v>
@@ -5053,28 +5053,28 @@
         <v>22.62</v>
       </c>
       <c r="M46">
-        <v>4.160772</v>
+        <v>4.255335000000001</v>
       </c>
       <c r="N46">
-        <v>18.459228</v>
+        <v>18.364665</v>
       </c>
       <c r="O46">
-        <v>2.7688842</v>
+        <v>2.75469975</v>
       </c>
       <c r="P46">
-        <v>15.6903438</v>
+        <v>15.60996525</v>
       </c>
       <c r="Q46">
-        <v>15.6953438</v>
+        <v>15.61496525</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1026432330972425</v>
+        <v>0.1035837966193888</v>
       </c>
       <c r="T46">
-        <v>0.7408578829104853</v>
+        <v>0.753116578656522</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.43649111270697</v>
+        <v>5.315680199091259</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07812333814066383</v>
+        <v>0.07808426574687188</v>
       </c>
       <c r="C47">
-        <v>106.753088216488</v>
+        <v>105.1329444784402</v>
       </c>
       <c r="D47">
-        <v>176.443088216488</v>
+        <v>176.5329444784402</v>
       </c>
       <c r="E47">
-        <v>39.75</v>
+        <v>41.45999999999999</v>
       </c>
       <c r="F47">
-        <v>76.95</v>
+        <v>78.66</v>
       </c>
       <c r="G47">
         <v>7.26</v>
@@ -5135,28 +5135,28 @@
         <v>22.62</v>
       </c>
       <c r="M47">
-        <v>4.255335000000001</v>
+        <v>4.349898</v>
       </c>
       <c r="N47">
-        <v>18.364665</v>
+        <v>18.270102</v>
       </c>
       <c r="O47">
-        <v>2.75469975</v>
+        <v>2.7405153</v>
       </c>
       <c r="P47">
-        <v>15.60996525</v>
+        <v>15.5295867</v>
       </c>
       <c r="Q47">
-        <v>15.61496525</v>
+        <v>15.5345867</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1035837966193888</v>
+        <v>0.1045591958275405</v>
       </c>
       <c r="T47">
-        <v>0.753116578656522</v>
+        <v>0.7658293001709308</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.315680199091259</v>
+        <v>5.200121933893623</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07808426574687188</v>
+        <v>0.07804519335307993</v>
       </c>
       <c r="C48">
-        <v>105.1329444784402</v>
+        <v>103.5128923082954</v>
       </c>
       <c r="D48">
-        <v>176.5329444784402</v>
+        <v>176.6228923082954</v>
       </c>
       <c r="E48">
-        <v>41.45999999999999</v>
+        <v>43.17</v>
       </c>
       <c r="F48">
-        <v>78.66</v>
+        <v>80.37</v>
       </c>
       <c r="G48">
         <v>7.26</v>
@@ -5217,28 +5217,28 @@
         <v>22.62</v>
       </c>
       <c r="M48">
-        <v>4.349898</v>
+        <v>4.444461</v>
       </c>
       <c r="N48">
-        <v>18.270102</v>
+        <v>18.175539</v>
       </c>
       <c r="O48">
-        <v>2.7405153</v>
+        <v>2.72633085</v>
       </c>
       <c r="P48">
-        <v>15.5295867</v>
+        <v>15.44920815</v>
       </c>
       <c r="Q48">
-        <v>15.5345867</v>
+        <v>15.45420815</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1045591958275405</v>
+        <v>0.105571402552981</v>
       </c>
       <c r="T48">
-        <v>0.7658293001709308</v>
+        <v>0.7790217470255056</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.200121933893623</v>
+        <v>5.089481041683119</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07804519335307993</v>
+        <v>0.07800612095928798</v>
       </c>
       <c r="C49">
-        <v>103.5128923082954</v>
+        <v>101.8929318460929</v>
       </c>
       <c r="D49">
-        <v>176.6228923082954</v>
+        <v>176.712931846093</v>
       </c>
       <c r="E49">
-        <v>43.17</v>
+        <v>44.88000000000001</v>
       </c>
       <c r="F49">
-        <v>80.37</v>
+        <v>82.08000000000001</v>
       </c>
       <c r="G49">
         <v>7.26</v>
@@ -5299,28 +5299,28 @@
         <v>22.62</v>
       </c>
       <c r="M49">
-        <v>4.444461</v>
+        <v>4.539024000000001</v>
       </c>
       <c r="N49">
-        <v>18.175539</v>
+        <v>18.080976</v>
       </c>
       <c r="O49">
-        <v>2.72633085</v>
+        <v>2.7121464</v>
       </c>
       <c r="P49">
-        <v>15.44920815</v>
+        <v>15.3688296</v>
       </c>
       <c r="Q49">
-        <v>15.45420815</v>
+        <v>15.3738296</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.105571402552981</v>
+        <v>0.106622540306323</v>
       </c>
       <c r="T49">
-        <v>0.7790217470255056</v>
+        <v>0.7927215956821796</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.089481041683119</v>
+        <v>4.983450186648053</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07800612095928798</v>
+        <v>0.07796704856549601</v>
       </c>
       <c r="C50">
-        <v>101.892931846093</v>
+        <v>100.2730632321584</v>
       </c>
       <c r="D50">
-        <v>176.712931846093</v>
+        <v>176.8030632321584</v>
       </c>
       <c r="E50">
-        <v>44.88</v>
+        <v>46.58999999999999</v>
       </c>
       <c r="F50">
-        <v>82.08</v>
+        <v>83.78999999999999</v>
       </c>
       <c r="G50">
         <v>7.26</v>
@@ -5381,28 +5381,28 @@
         <v>22.62</v>
       </c>
       <c r="M50">
-        <v>4.539024</v>
+        <v>4.633586999999999</v>
       </c>
       <c r="N50">
-        <v>18.080976</v>
+        <v>17.986413</v>
       </c>
       <c r="O50">
-        <v>2.7121464</v>
+        <v>2.69796195</v>
       </c>
       <c r="P50">
-        <v>15.3688296</v>
+        <v>15.28845105</v>
       </c>
       <c r="Q50">
-        <v>15.3738296</v>
+        <v>15.29345105</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.106622540306323</v>
+        <v>0.1077148991480314</v>
       </c>
       <c r="T50">
-        <v>0.7927215956821796</v>
+        <v>0.8069586933057818</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.983450186648055</v>
+        <v>4.881747121614422</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07796704856549601</v>
+        <v>0.07792797617170406</v>
       </c>
       <c r="C51">
-        <v>100.2730632321584</v>
+        <v>98.65328660710327</v>
       </c>
       <c r="D51">
-        <v>176.8030632321584</v>
+        <v>176.8932866071033</v>
       </c>
       <c r="E51">
-        <v>46.58999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="F51">
-        <v>83.78999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="G51">
         <v>7.26</v>
@@ -5463,28 +5463,28 @@
         <v>22.62</v>
       </c>
       <c r="M51">
-        <v>4.633586999999999</v>
+        <v>4.72815</v>
       </c>
       <c r="N51">
-        <v>17.986413</v>
+        <v>17.89185</v>
       </c>
       <c r="O51">
-        <v>2.69796195</v>
+        <v>2.6837775</v>
       </c>
       <c r="P51">
-        <v>15.28845105</v>
+        <v>15.2080725</v>
       </c>
       <c r="Q51">
-        <v>15.29345105</v>
+        <v>15.2130725</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1077148991480314</v>
+        <v>0.1088509523434081</v>
       </c>
       <c r="T51">
-        <v>0.8069586933057818</v>
+        <v>0.8217652748343285</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.881747121614422</v>
+        <v>4.784112179182133</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07792797617170406</v>
+        <v>0.07788890377791212</v>
       </c>
       <c r="C52">
-        <v>98.65328660710327</v>
+        <v>97.03360211182655</v>
       </c>
       <c r="D52">
-        <v>176.8932866071033</v>
+        <v>176.9836021118266</v>
       </c>
       <c r="E52">
-        <v>48.3</v>
+        <v>50.01000000000001</v>
       </c>
       <c r="F52">
-        <v>85.5</v>
+        <v>87.21000000000001</v>
       </c>
       <c r="G52">
         <v>7.26</v>
@@ -5545,28 +5545,28 @@
         <v>22.62</v>
       </c>
       <c r="M52">
-        <v>4.72815</v>
+        <v>4.822713</v>
       </c>
       <c r="N52">
-        <v>17.89185</v>
+        <v>17.797287</v>
       </c>
       <c r="O52">
-        <v>2.6837775</v>
+        <v>2.66959305</v>
       </c>
       <c r="P52">
-        <v>15.2080725</v>
+        <v>15.12769395</v>
       </c>
       <c r="Q52">
-        <v>15.2130725</v>
+        <v>15.13269395</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1088509523434081</v>
+        <v>0.1100333750569635</v>
       </c>
       <c r="T52">
-        <v>0.8217652748343285</v>
+        <v>0.8371762066293462</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.784112179182133</v>
+        <v>4.690306058021699</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07788890377791212</v>
+        <v>0.07784983138412016</v>
       </c>
       <c r="C53">
-        <v>97.03360211182655</v>
+        <v>95.41400988751501</v>
       </c>
       <c r="D53">
-        <v>176.9836021118266</v>
+        <v>177.074009887515</v>
       </c>
       <c r="E53">
-        <v>50.01000000000001</v>
+        <v>51.72</v>
       </c>
       <c r="F53">
-        <v>87.21000000000001</v>
+        <v>88.92</v>
       </c>
       <c r="G53">
         <v>7.26</v>
@@ -5627,28 +5627,28 @@
         <v>22.62</v>
       </c>
       <c r="M53">
-        <v>4.822713</v>
+        <v>4.917276</v>
       </c>
       <c r="N53">
-        <v>17.797287</v>
+        <v>17.702724</v>
       </c>
       <c r="O53">
-        <v>2.66959305</v>
+        <v>2.6554086</v>
       </c>
       <c r="P53">
-        <v>15.12769395</v>
+        <v>15.0473154</v>
       </c>
       <c r="Q53">
-        <v>15.13269395</v>
+        <v>15.0523154</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1100333750569635</v>
+        <v>0.1112650653835837</v>
       </c>
       <c r="T53">
-        <v>0.8371762066293462</v>
+        <v>0.8532292605824897</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.690306058021699</v>
+        <v>4.600107864598204</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07784983138412016</v>
+        <v>0.07781075899032822</v>
       </c>
       <c r="C54">
-        <v>95.41400988751501</v>
+        <v>93.794510075644</v>
       </c>
       <c r="D54">
-        <v>177.074009887515</v>
+        <v>177.164510075644</v>
       </c>
       <c r="E54">
-        <v>51.72</v>
+        <v>53.43000000000001</v>
       </c>
       <c r="F54">
-        <v>88.92</v>
+        <v>90.63000000000001</v>
       </c>
       <c r="G54">
         <v>7.26</v>
@@ -5709,28 +5709,28 @@
         <v>22.62</v>
       </c>
       <c r="M54">
-        <v>4.917276</v>
+        <v>5.011839000000001</v>
       </c>
       <c r="N54">
-        <v>17.702724</v>
+        <v>17.608161</v>
       </c>
       <c r="O54">
-        <v>2.6554086</v>
+        <v>2.64122415</v>
       </c>
       <c r="P54">
-        <v>15.0473154</v>
+        <v>14.96693685</v>
       </c>
       <c r="Q54">
-        <v>15.0523154</v>
+        <v>14.97193685</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1112650653835837</v>
+        <v>0.1125491680645281</v>
       </c>
       <c r="T54">
-        <v>0.8532292605824897</v>
+        <v>0.8699654232144903</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.600107864598204</v>
+        <v>4.513313376586916</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07781075899032822</v>
+        <v>0.07891918659653625</v>
       </c>
       <c r="C55">
-        <v>93.794510075644</v>
+        <v>89.55254818108529</v>
       </c>
       <c r="D55">
-        <v>177.164510075644</v>
+        <v>174.6325481810853</v>
       </c>
       <c r="E55">
-        <v>53.43000000000001</v>
+        <v>55.14</v>
       </c>
       <c r="F55">
-        <v>90.63000000000001</v>
+        <v>92.34</v>
       </c>
       <c r="G55">
         <v>7.26</v>
@@ -5791,45 +5791,45 @@
         <v>22.62</v>
       </c>
       <c r="M55">
-        <v>5.011839000000001</v>
+        <v>5.337252</v>
       </c>
       <c r="N55">
-        <v>17.608161</v>
+        <v>17.282748</v>
       </c>
       <c r="O55">
-        <v>2.64122415</v>
+        <v>2.5924122</v>
       </c>
       <c r="P55">
-        <v>14.96693685</v>
+        <v>14.6903358</v>
       </c>
       <c r="Q55">
-        <v>14.97193685</v>
+        <v>14.6953358</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1125491680645281</v>
+        <v>0.113889101296818</v>
       </c>
       <c r="T55">
-        <v>0.8699654232144903</v>
+        <v>0.8874292450913607</v>
       </c>
       <c r="U55">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V55">
         <v>0.15</v>
       </c>
       <c r="W55">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>4.513313376586916</v>
+        <v>4.238136029552287</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07891918659653625</v>
+        <v>0.07890136420274431</v>
       </c>
       <c r="C56">
-        <v>89.55254818108529</v>
+        <v>87.8826869585194</v>
       </c>
       <c r="D56">
-        <v>174.6325481810853</v>
+        <v>174.6726869585194</v>
       </c>
       <c r="E56">
-        <v>55.14</v>
+        <v>56.85000000000001</v>
       </c>
       <c r="F56">
-        <v>92.34</v>
+        <v>94.05000000000001</v>
       </c>
       <c r="G56">
         <v>7.26</v>
@@ -5873,28 +5873,28 @@
         <v>22.62</v>
       </c>
       <c r="M56">
-        <v>5.337252</v>
+        <v>5.436090000000001</v>
       </c>
       <c r="N56">
-        <v>17.282748</v>
+        <v>17.18391</v>
       </c>
       <c r="O56">
-        <v>2.5924122</v>
+        <v>2.5775865</v>
       </c>
       <c r="P56">
-        <v>14.6903358</v>
+        <v>14.6063235</v>
       </c>
       <c r="Q56">
-        <v>14.6953358</v>
+        <v>14.6113235</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.113889101296818</v>
+        <v>0.1152885871172096</v>
       </c>
       <c r="T56">
-        <v>0.8874292450913607</v>
+        <v>0.9056692368294252</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.238136029552287</v>
+        <v>4.161079010833154</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07890136420274431</v>
+        <v>0.07888354180895235</v>
       </c>
       <c r="C57">
-        <v>87.8826869585194</v>
+        <v>86.21284419175531</v>
       </c>
       <c r="D57">
-        <v>174.6726869585194</v>
+        <v>174.7128441917553</v>
       </c>
       <c r="E57">
-        <v>56.85000000000001</v>
+        <v>58.56</v>
       </c>
       <c r="F57">
-        <v>94.05000000000001</v>
+        <v>95.76000000000001</v>
       </c>
       <c r="G57">
         <v>7.26</v>
@@ -5955,28 +5955,28 @@
         <v>22.62</v>
       </c>
       <c r="M57">
-        <v>5.436090000000001</v>
+        <v>5.534928000000001</v>
       </c>
       <c r="N57">
-        <v>17.18391</v>
+        <v>17.085072</v>
       </c>
       <c r="O57">
-        <v>2.5775865</v>
+        <v>2.5627608</v>
       </c>
       <c r="P57">
-        <v>14.6063235</v>
+        <v>14.5223112</v>
       </c>
       <c r="Q57">
-        <v>14.6113235</v>
+        <v>14.5273112</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1152885871172096</v>
+        <v>0.1167516859294372</v>
       </c>
       <c r="T57">
-        <v>0.9056692368294252</v>
+        <v>0.924738319101038</v>
       </c>
       <c r="U57">
         <v>0.0578</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.161079010833154</v>
+        <v>4.086774028496848</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07888354180895235</v>
+        <v>0.07886571941516041</v>
       </c>
       <c r="C58">
-        <v>86.21284419175531</v>
+        <v>84.54301989352491</v>
       </c>
       <c r="D58">
-        <v>174.7128441917553</v>
+        <v>174.7530198935249</v>
       </c>
       <c r="E58">
-        <v>58.56</v>
+        <v>60.27000000000001</v>
       </c>
       <c r="F58">
-        <v>95.76000000000001</v>
+        <v>97.47000000000001</v>
       </c>
       <c r="G58">
         <v>7.26</v>
@@ -6037,28 +6037,28 @@
         <v>22.62</v>
       </c>
       <c r="M58">
-        <v>5.534928000000001</v>
+        <v>5.633766000000001</v>
       </c>
       <c r="N58">
-        <v>17.085072</v>
+        <v>16.986234</v>
       </c>
       <c r="O58">
-        <v>2.5627608</v>
+        <v>2.5479351</v>
       </c>
       <c r="P58">
-        <v>14.5223112</v>
+        <v>14.4382989</v>
       </c>
       <c r="Q58">
-        <v>14.5273112</v>
+        <v>14.4432989</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1167516859294372</v>
+        <v>0.1182828358492102</v>
       </c>
       <c r="T58">
-        <v>0.924738319101038</v>
+        <v>0.9446943354317957</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.086774028496848</v>
+        <v>4.015076238523218</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07886571941516041</v>
+        <v>0.08057339702136845</v>
       </c>
       <c r="C59">
-        <v>84.54301989352491</v>
+        <v>79.06565096249497</v>
       </c>
       <c r="D59">
-        <v>174.7530198935249</v>
+        <v>170.985650962495</v>
       </c>
       <c r="E59">
-        <v>60.27000000000001</v>
+        <v>61.98</v>
       </c>
       <c r="F59">
-        <v>97.47000000000001</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="G59">
         <v>7.26</v>
@@ -6119,45 +6119,45 @@
         <v>22.62</v>
       </c>
       <c r="M59">
-        <v>5.633766000000001</v>
+        <v>6.079734</v>
       </c>
       <c r="N59">
-        <v>16.986234</v>
+        <v>16.540266</v>
       </c>
       <c r="O59">
-        <v>2.5479351</v>
+        <v>2.4810399</v>
       </c>
       <c r="P59">
-        <v>14.4382989</v>
+        <v>14.0592261</v>
       </c>
       <c r="Q59">
-        <v>14.4432989</v>
+        <v>14.0642261</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1182828358492102</v>
+        <v>0.1198868976699249</v>
       </c>
       <c r="T59">
-        <v>0.9446943354317957</v>
+        <v>0.9656006382544942</v>
       </c>
       <c r="U59">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V59">
         <v>0.15</v>
       </c>
       <c r="W59">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>4.015076238523218</v>
+        <v>3.720557511233222</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08057339702136844</v>
+        <v>0.08058532462757649</v>
       </c>
       <c r="C60">
-        <v>79.06565096249501</v>
+        <v>77.3299082001446</v>
       </c>
       <c r="D60">
-        <v>170.985650962495</v>
+        <v>170.9599082001446</v>
       </c>
       <c r="E60">
-        <v>61.97999999999999</v>
+        <v>63.69</v>
       </c>
       <c r="F60">
-        <v>99.17999999999999</v>
+        <v>100.89</v>
       </c>
       <c r="G60">
         <v>7.26</v>
@@ -6201,28 +6201,28 @@
         <v>22.62</v>
       </c>
       <c r="M60">
-        <v>6.079733999999999</v>
+        <v>6.184557</v>
       </c>
       <c r="N60">
-        <v>16.540266</v>
+        <v>16.435443</v>
       </c>
       <c r="O60">
-        <v>2.4810399</v>
+        <v>2.46531645</v>
       </c>
       <c r="P60">
-        <v>14.0592261</v>
+        <v>13.97012655</v>
       </c>
       <c r="Q60">
-        <v>14.0642261</v>
+        <v>13.97512655</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1198868976699249</v>
+        <v>0.1215692064087232</v>
       </c>
       <c r="T60">
-        <v>0.9656006382544939</v>
+        <v>0.98752676072708</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.720557511233222</v>
+        <v>3.657497214432659</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08058532462757649</v>
+        <v>0.08059725223378454</v>
       </c>
       <c r="C61">
-        <v>77.3299082001446</v>
+        <v>75.59417318803585</v>
       </c>
       <c r="D61">
-        <v>170.9599082001446</v>
+        <v>170.9341731880359</v>
       </c>
       <c r="E61">
-        <v>63.69</v>
+        <v>65.39999999999999</v>
       </c>
       <c r="F61">
-        <v>100.89</v>
+        <v>102.6</v>
       </c>
       <c r="G61">
         <v>7.26</v>
@@ -6283,28 +6283,28 @@
         <v>22.62</v>
       </c>
       <c r="M61">
-        <v>6.184557</v>
+        <v>6.28938</v>
       </c>
       <c r="N61">
-        <v>16.435443</v>
+        <v>16.33062</v>
       </c>
       <c r="O61">
-        <v>2.46531645</v>
+        <v>2.449593000000001</v>
       </c>
       <c r="P61">
-        <v>13.97012655</v>
+        <v>13.881027</v>
       </c>
       <c r="Q61">
-        <v>13.97512655</v>
+        <v>13.886027</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1215692064087232</v>
+        <v>0.1233356305844613</v>
       </c>
       <c r="T61">
-        <v>0.98752676072708</v>
+        <v>1.010549189323296</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.657497214432659</v>
+        <v>3.596538927525448</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08059725223378454</v>
+        <v>0.08060917983999259</v>
       </c>
       <c r="C62">
-        <v>75.59417318803585</v>
+        <v>73.85844592266926</v>
       </c>
       <c r="D62">
-        <v>170.9341731880359</v>
+        <v>170.9084459226693</v>
       </c>
       <c r="E62">
-        <v>65.39999999999999</v>
+        <v>67.11</v>
       </c>
       <c r="F62">
-        <v>102.6</v>
+        <v>104.31</v>
       </c>
       <c r="G62">
         <v>7.26</v>
@@ -6365,28 +6365,28 @@
         <v>22.62</v>
       </c>
       <c r="M62">
-        <v>6.28938</v>
+        <v>6.394203</v>
       </c>
       <c r="N62">
-        <v>16.33062</v>
+        <v>16.225797</v>
       </c>
       <c r="O62">
-        <v>2.449593000000001</v>
+        <v>2.43386955</v>
       </c>
       <c r="P62">
-        <v>13.881027</v>
+        <v>13.79192745</v>
       </c>
       <c r="Q62">
-        <v>13.886027</v>
+        <v>13.79692745</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1233356305844613</v>
+        <v>0.1251926406153656</v>
       </c>
       <c r="T62">
-        <v>1.010549189323296</v>
+        <v>1.03475225528342</v>
       </c>
       <c r="U62">
         <v>0.0613</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.596538927525448</v>
+        <v>3.53757927297585</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08060917983999259</v>
+        <v>0.08209670744620064</v>
       </c>
       <c r="C63">
-        <v>73.85844592266926</v>
+        <v>68.99951143728212</v>
       </c>
       <c r="D63">
-        <v>170.9084459226693</v>
+        <v>167.7595114372821</v>
       </c>
       <c r="E63">
-        <v>67.11</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="F63">
-        <v>104.31</v>
+        <v>106.02</v>
       </c>
       <c r="G63">
         <v>7.26</v>
@@ -6447,45 +6447,45 @@
         <v>22.62</v>
       </c>
       <c r="M63">
-        <v>6.394203</v>
+        <v>6.795882</v>
       </c>
       <c r="N63">
-        <v>16.225797</v>
+        <v>15.824118</v>
       </c>
       <c r="O63">
-        <v>2.43386955</v>
+        <v>2.3736177</v>
       </c>
       <c r="P63">
-        <v>13.79192745</v>
+        <v>13.4505003</v>
       </c>
       <c r="Q63">
-        <v>13.79692745</v>
+        <v>13.4555003</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1251926406153656</v>
+        <v>0.1271473880163175</v>
       </c>
       <c r="T63">
-        <v>1.03475225528342</v>
+        <v>1.060229166820392</v>
       </c>
       <c r="U63">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V63">
         <v>0.15</v>
       </c>
       <c r="W63">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>3.53757927297585</v>
+        <v>3.328486280368023</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08209670744620064</v>
+        <v>0.08213243505240869</v>
       </c>
       <c r="C64">
-        <v>68.99951143728212</v>
+        <v>67.2153062965492</v>
       </c>
       <c r="D64">
-        <v>167.7595114372821</v>
+        <v>167.6853062965492</v>
       </c>
       <c r="E64">
-        <v>68.81999999999999</v>
+        <v>70.53</v>
       </c>
       <c r="F64">
-        <v>106.02</v>
+        <v>107.73</v>
       </c>
       <c r="G64">
         <v>7.26</v>
@@ -6529,28 +6529,28 @@
         <v>22.62</v>
       </c>
       <c r="M64">
-        <v>6.795882</v>
+        <v>6.905493000000001</v>
       </c>
       <c r="N64">
-        <v>15.824118</v>
+        <v>15.714507</v>
       </c>
       <c r="O64">
-        <v>2.3736177</v>
+        <v>2.35717605</v>
       </c>
       <c r="P64">
-        <v>13.4505003</v>
+        <v>13.35733095</v>
       </c>
       <c r="Q64">
-        <v>13.4555003</v>
+        <v>13.36233095</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1271473880163175</v>
+        <v>0.1292077974389424</v>
       </c>
       <c r="T64">
-        <v>1.060229166820392</v>
+        <v>1.087083208710715</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.328486280368023</v>
+        <v>3.275653164806625</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08213243505240869</v>
+        <v>0.08216816265861673</v>
       </c>
       <c r="C65">
-        <v>67.2153062965492</v>
+        <v>65.43116677317889</v>
       </c>
       <c r="D65">
-        <v>167.6853062965492</v>
+        <v>167.6111667731789</v>
       </c>
       <c r="E65">
-        <v>70.53</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="F65">
-        <v>107.73</v>
+        <v>109.44</v>
       </c>
       <c r="G65">
         <v>7.26</v>
@@ -6611,28 +6611,28 @@
         <v>22.62</v>
       </c>
       <c r="M65">
-        <v>6.905493000000001</v>
+        <v>7.015104</v>
       </c>
       <c r="N65">
-        <v>15.714507</v>
+        <v>15.604896</v>
       </c>
       <c r="O65">
-        <v>2.35717605</v>
+        <v>2.3407344</v>
       </c>
       <c r="P65">
-        <v>13.35733095</v>
+        <v>13.2641616</v>
       </c>
       <c r="Q65">
-        <v>13.36233095</v>
+        <v>13.2691616</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1292077974389424</v>
+        <v>0.1313826740517131</v>
       </c>
       <c r="T65">
-        <v>1.087083208710715</v>
+        <v>1.115429141817166</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.275653164806625</v>
+        <v>3.224471084106522</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08216816265861673</v>
+        <v>0.08220389026482479</v>
       </c>
       <c r="C66">
-        <v>65.43116677317889</v>
+        <v>63.64709278017429</v>
       </c>
       <c r="D66">
-        <v>167.6111667731789</v>
+        <v>167.5370927801743</v>
       </c>
       <c r="E66">
-        <v>72.23999999999999</v>
+        <v>73.95</v>
       </c>
       <c r="F66">
-        <v>109.44</v>
+        <v>111.15</v>
       </c>
       <c r="G66">
         <v>7.26</v>
@@ -6693,28 +6693,28 @@
         <v>22.62</v>
       </c>
       <c r="M66">
-        <v>7.015104</v>
+        <v>7.124715000000001</v>
       </c>
       <c r="N66">
-        <v>15.604896</v>
+        <v>15.495285</v>
       </c>
       <c r="O66">
-        <v>2.3407344</v>
+        <v>2.32429275</v>
       </c>
       <c r="P66">
-        <v>13.2641616</v>
+        <v>13.17099225</v>
       </c>
       <c r="Q66">
-        <v>13.2691616</v>
+        <v>13.17599225</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1313826740517131</v>
+        <v>0.1336818293280708</v>
       </c>
       <c r="T66">
-        <v>1.115429141817166</v>
+        <v>1.145394842529701</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.224471084106522</v>
+        <v>3.174863836658729</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08220389026482479</v>
+        <v>0.08223961787103282</v>
       </c>
       <c r="C67">
-        <v>63.64709278017429</v>
+        <v>61.86308423069259</v>
       </c>
       <c r="D67">
-        <v>167.5370927801743</v>
+        <v>167.4630842306926</v>
       </c>
       <c r="E67">
-        <v>73.95</v>
+        <v>75.66</v>
       </c>
       <c r="F67">
-        <v>111.15</v>
+        <v>112.86</v>
       </c>
       <c r="G67">
         <v>7.26</v>
@@ -6775,28 +6775,28 @@
         <v>22.62</v>
       </c>
       <c r="M67">
-        <v>7.124715000000001</v>
+        <v>7.234326</v>
       </c>
       <c r="N67">
-        <v>15.495285</v>
+        <v>15.385674</v>
       </c>
       <c r="O67">
-        <v>2.32429275</v>
+        <v>2.3078511</v>
       </c>
       <c r="P67">
-        <v>13.17099225</v>
+        <v>13.0778229</v>
       </c>
       <c r="Q67">
-        <v>13.17599225</v>
+        <v>13.0828229</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1336818293280708</v>
+        <v>0.1361162290324495</v>
       </c>
       <c r="T67">
-        <v>1.145394842529701</v>
+        <v>1.177123231519444</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.174863836658729</v>
+        <v>3.126759839133598</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08223961787103282</v>
+        <v>0.08227534547724089</v>
       </c>
       <c r="C68">
-        <v>61.86308423069259</v>
+        <v>60.079141038044</v>
       </c>
       <c r="D68">
-        <v>167.4630842306926</v>
+        <v>167.389141038044</v>
       </c>
       <c r="E68">
-        <v>75.66</v>
+        <v>77.37</v>
       </c>
       <c r="F68">
-        <v>112.86</v>
+        <v>114.57</v>
       </c>
       <c r="G68">
         <v>7.26</v>
@@ -6857,28 +6857,28 @@
         <v>22.62</v>
       </c>
       <c r="M68">
-        <v>7.234326</v>
+        <v>7.343937000000001</v>
       </c>
       <c r="N68">
-        <v>15.385674</v>
+        <v>15.276063</v>
       </c>
       <c r="O68">
-        <v>2.3078511</v>
+        <v>2.29140945</v>
       </c>
       <c r="P68">
-        <v>13.0778229</v>
+        <v>12.98465355</v>
       </c>
       <c r="Q68">
-        <v>13.0828229</v>
+        <v>12.98965355</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1361162290324495</v>
+        <v>0.1386981681128512</v>
       </c>
       <c r="T68">
-        <v>1.177123231519444</v>
+        <v>1.210774553175231</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.126759839133598</v>
+        <v>3.080091781833096</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08227534547724089</v>
+        <v>0.08231107308344893</v>
       </c>
       <c r="C69">
-        <v>60.079141038044</v>
+        <v>58.29526311569209</v>
       </c>
       <c r="D69">
-        <v>167.389141038044</v>
+        <v>167.3152631156921</v>
       </c>
       <c r="E69">
-        <v>77.37</v>
+        <v>79.08000000000001</v>
       </c>
       <c r="F69">
-        <v>114.57</v>
+        <v>116.28</v>
       </c>
       <c r="G69">
         <v>7.26</v>
@@ -6939,28 +6939,28 @@
         <v>22.62</v>
       </c>
       <c r="M69">
-        <v>7.343937000000001</v>
+        <v>7.453548000000001</v>
       </c>
       <c r="N69">
-        <v>15.276063</v>
+        <v>15.166452</v>
       </c>
       <c r="O69">
-        <v>2.29140945</v>
+        <v>2.2749678</v>
       </c>
       <c r="P69">
-        <v>12.98465355</v>
+        <v>12.8914842</v>
       </c>
       <c r="Q69">
-        <v>12.98965355</v>
+        <v>12.8964842</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1386981681128512</v>
+        <v>0.1414414783857779</v>
       </c>
       <c r="T69">
-        <v>1.210774553175231</v>
+        <v>1.246529082434505</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.080091781833096</v>
+        <v>3.034796314453197</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08231107308344893</v>
+        <v>0.08692150068965698</v>
       </c>
       <c r="C70">
-        <v>58.29526311569209</v>
+        <v>47.56946599149296</v>
       </c>
       <c r="D70">
-        <v>167.3152631156921</v>
+        <v>158.299465991493</v>
       </c>
       <c r="E70">
-        <v>79.08000000000001</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="F70">
-        <v>116.28</v>
+        <v>117.99</v>
       </c>
       <c r="G70">
         <v>7.26</v>
@@ -7021,45 +7021,45 @@
         <v>22.62</v>
       </c>
       <c r="M70">
-        <v>7.453548000000001</v>
+        <v>8.483481000000001</v>
       </c>
       <c r="N70">
-        <v>15.166452</v>
+        <v>14.136519</v>
       </c>
       <c r="O70">
-        <v>2.2749678</v>
+        <v>2.12047785</v>
       </c>
       <c r="P70">
-        <v>12.8914842</v>
+        <v>12.01604115</v>
       </c>
       <c r="Q70">
-        <v>12.8964842</v>
+        <v>12.02104115</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1414414783857779</v>
+        <v>0.1443617764182483</v>
       </c>
       <c r="T70">
-        <v>1.246529082434505</v>
+        <v>1.284590355516958</v>
       </c>
       <c r="U70">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V70">
         <v>0.15</v>
       </c>
       <c r="W70">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y70">
-        <v>3.034796314453197</v>
+        <v>2.66635830268259</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08692150068965698</v>
+        <v>0.08702352829586502</v>
       </c>
       <c r="C71">
-        <v>47.56946599149296</v>
+        <v>45.67092450008855</v>
       </c>
       <c r="D71">
-        <v>158.299465991493</v>
+        <v>158.1109245000886</v>
       </c>
       <c r="E71">
-        <v>80.79000000000001</v>
+        <v>82.50000000000001</v>
       </c>
       <c r="F71">
-        <v>117.99</v>
+        <v>119.7</v>
       </c>
       <c r="G71">
         <v>7.26</v>
@@ -7103,28 +7103,28 @@
         <v>22.62</v>
       </c>
       <c r="M71">
-        <v>8.483481000000001</v>
+        <v>8.606430000000001</v>
       </c>
       <c r="N71">
-        <v>14.136519</v>
+        <v>14.01357</v>
       </c>
       <c r="O71">
-        <v>2.12047785</v>
+        <v>2.1020355</v>
       </c>
       <c r="P71">
-        <v>12.01604115</v>
+        <v>11.9115345</v>
       </c>
       <c r="Q71">
-        <v>12.02104115</v>
+        <v>11.9165345</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1443617764182483</v>
+        <v>0.1474767609862168</v>
       </c>
       <c r="T71">
-        <v>1.284590355516958</v>
+        <v>1.325189046804908</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.66635830268259</v>
+        <v>2.628267469787124</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08702352829586502</v>
+        <v>0.08712555590207308</v>
       </c>
       <c r="C72">
-        <v>45.67092450008855</v>
+        <v>43.77283159649268</v>
       </c>
       <c r="D72">
-        <v>158.1109245000886</v>
+        <v>157.9228315964927</v>
       </c>
       <c r="E72">
-        <v>82.50000000000001</v>
+        <v>84.21000000000001</v>
       </c>
       <c r="F72">
-        <v>119.7</v>
+        <v>121.41</v>
       </c>
       <c r="G72">
         <v>7.26</v>
@@ -7185,28 +7185,28 @@
         <v>22.62</v>
       </c>
       <c r="M72">
-        <v>8.606430000000001</v>
+        <v>8.729379000000002</v>
       </c>
       <c r="N72">
-        <v>14.01357</v>
+        <v>13.890621</v>
       </c>
       <c r="O72">
-        <v>2.1020355</v>
+        <v>2.08359315</v>
       </c>
       <c r="P72">
-        <v>11.9115345</v>
+        <v>11.80702785</v>
       </c>
       <c r="Q72">
-        <v>11.9165345</v>
+        <v>11.81202785</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1474767609862168</v>
+        <v>0.1508065720761141</v>
       </c>
       <c r="T72">
-        <v>1.325189046804908</v>
+        <v>1.368587647836855</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.628267469787124</v>
+        <v>2.591249618099981</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08712555590207306</v>
+        <v>0.08722758350828111</v>
       </c>
       <c r="C73">
-        <v>43.77283159649272</v>
+        <v>41.87518568165224</v>
       </c>
       <c r="D73">
-        <v>157.9228315964927</v>
+        <v>157.7351856816522</v>
       </c>
       <c r="E73">
-        <v>84.20999999999999</v>
+        <v>85.91999999999999</v>
       </c>
       <c r="F73">
-        <v>121.41</v>
+        <v>123.12</v>
       </c>
       <c r="G73">
         <v>7.26</v>
@@ -7267,28 +7267,28 @@
         <v>22.62</v>
       </c>
       <c r="M73">
-        <v>8.729379</v>
+        <v>8.852328</v>
       </c>
       <c r="N73">
-        <v>13.890621</v>
+        <v>13.767672</v>
       </c>
       <c r="O73">
-        <v>2.08359315</v>
+        <v>2.0651508</v>
       </c>
       <c r="P73">
-        <v>11.80702785</v>
+        <v>11.7025212</v>
       </c>
       <c r="Q73">
-        <v>11.81202785</v>
+        <v>11.7075212</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.150806572076114</v>
+        <v>0.1543742268152897</v>
       </c>
       <c r="T73">
-        <v>1.368587647836854</v>
+        <v>1.415086148942512</v>
       </c>
       <c r="U73">
         <v>0.07190000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.591249618099982</v>
+        <v>2.555260040070816</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.08722758350828111</v>
+        <v>0.08732961111448917</v>
       </c>
       <c r="C74">
-        <v>41.87518568165224</v>
+        <v>39.97798516410494</v>
       </c>
       <c r="D74">
-        <v>157.7351856816522</v>
+        <v>157.5479851641049</v>
       </c>
       <c r="E74">
-        <v>85.91999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="F74">
-        <v>123.12</v>
+        <v>124.83</v>
       </c>
       <c r="G74">
         <v>7.26</v>
@@ -7349,28 +7349,28 @@
         <v>22.62</v>
       </c>
       <c r="M74">
-        <v>8.852328</v>
+        <v>8.975277</v>
       </c>
       <c r="N74">
-        <v>13.767672</v>
+        <v>13.644723</v>
       </c>
       <c r="O74">
-        <v>2.0651508</v>
+        <v>2.04670845</v>
       </c>
       <c r="P74">
-        <v>11.7025212</v>
+        <v>11.59801455</v>
       </c>
       <c r="Q74">
-        <v>11.7075212</v>
+        <v>11.60301455</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1543742268152897</v>
+        <v>0.1582061522758858</v>
       </c>
       <c r="T74">
-        <v>1.415086148942512</v>
+        <v>1.465028983463402</v>
       </c>
       <c r="U74">
         <v>0.07190000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.555260040070816</v>
+        <v>2.520256477878065</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08732961111448917</v>
+        <v>0.0898847387206972</v>
       </c>
       <c r="C75">
-        <v>39.97798516410494</v>
+        <v>33.72055165827521</v>
       </c>
       <c r="D75">
-        <v>157.5479851641049</v>
+        <v>153.0005516582752</v>
       </c>
       <c r="E75">
-        <v>87.63</v>
+        <v>89.33999999999999</v>
       </c>
       <c r="F75">
-        <v>124.83</v>
+        <v>126.54</v>
       </c>
       <c r="G75">
         <v>7.26</v>
@@ -7431,45 +7431,45 @@
         <v>22.62</v>
       </c>
       <c r="M75">
-        <v>8.975277</v>
+        <v>9.591732</v>
       </c>
       <c r="N75">
-        <v>13.644723</v>
+        <v>13.028268</v>
       </c>
       <c r="O75">
-        <v>2.04670845</v>
+        <v>1.9542402</v>
       </c>
       <c r="P75">
-        <v>11.59801455</v>
+        <v>11.0740278</v>
       </c>
       <c r="Q75">
-        <v>11.60301455</v>
+        <v>11.0790278</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1582061522758858</v>
+        <v>0.1623328412334508</v>
       </c>
       <c r="T75">
-        <v>1.465028983463402</v>
+        <v>1.5188135744859</v>
       </c>
       <c r="U75">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V75">
         <v>0.15</v>
       </c>
       <c r="W75">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y75">
-        <v>2.520256477878065</v>
+        <v>2.358281069571168</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0898847387206972</v>
+        <v>0.09001991632690526</v>
       </c>
       <c r="C76">
-        <v>33.72055165827521</v>
+        <v>31.77727247512786</v>
       </c>
       <c r="D76">
-        <v>153.0005516582752</v>
+        <v>152.7672724751279</v>
       </c>
       <c r="E76">
-        <v>89.33999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="F76">
-        <v>126.54</v>
+        <v>128.25</v>
       </c>
       <c r="G76">
         <v>7.26</v>
@@ -7513,28 +7513,28 @@
         <v>22.62</v>
       </c>
       <c r="M76">
-        <v>9.591732</v>
+        <v>9.721350000000001</v>
       </c>
       <c r="N76">
-        <v>13.028268</v>
+        <v>12.89865</v>
       </c>
       <c r="O76">
-        <v>1.9542402</v>
+        <v>1.9347975</v>
       </c>
       <c r="P76">
-        <v>11.0740278</v>
+        <v>10.9638525</v>
       </c>
       <c r="Q76">
-        <v>11.0790278</v>
+        <v>10.9688525</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1623328412334508</v>
+        <v>0.166789665307621</v>
       </c>
       <c r="T76">
-        <v>1.5188135744859</v>
+        <v>1.576900932790198</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.358281069571168</v>
+        <v>2.326837321976886</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09001991632690526</v>
+        <v>0.09015509393311331</v>
       </c>
       <c r="C77">
-        <v>31.77727247512786</v>
+        <v>29.83470356825552</v>
       </c>
       <c r="D77">
-        <v>152.7672724751279</v>
+        <v>152.5347035682555</v>
       </c>
       <c r="E77">
-        <v>91.05</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="F77">
-        <v>128.25</v>
+        <v>129.96</v>
       </c>
       <c r="G77">
         <v>7.26</v>
@@ -7595,28 +7595,28 @@
         <v>22.62</v>
       </c>
       <c r="M77">
-        <v>9.721350000000001</v>
+        <v>9.850968000000002</v>
       </c>
       <c r="N77">
-        <v>12.89865</v>
+        <v>12.769032</v>
       </c>
       <c r="O77">
-        <v>1.9347975</v>
+        <v>1.9153548</v>
       </c>
       <c r="P77">
-        <v>10.9638525</v>
+        <v>10.8536772</v>
       </c>
       <c r="Q77">
-        <v>10.9688525</v>
+        <v>10.8586772</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.166789665307621</v>
+        <v>0.1716178913879721</v>
       </c>
       <c r="T77">
-        <v>1.576900932790198</v>
+        <v>1.63982890428652</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.326837321976886</v>
+        <v>2.296221041424558</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09015509393311331</v>
+        <v>0.09029027153932136</v>
       </c>
       <c r="C78">
-        <v>29.83470356825552</v>
+        <v>27.89284169867105</v>
       </c>
       <c r="D78">
-        <v>152.5347035682555</v>
+        <v>152.3028416986711</v>
       </c>
       <c r="E78">
-        <v>92.76000000000001</v>
+        <v>94.47000000000001</v>
       </c>
       <c r="F78">
-        <v>129.96</v>
+        <v>131.67</v>
       </c>
       <c r="G78">
         <v>7.26</v>
@@ -7677,28 +7677,28 @@
         <v>22.62</v>
       </c>
       <c r="M78">
-        <v>9.850968000000002</v>
+        <v>9.980586000000002</v>
       </c>
       <c r="N78">
-        <v>12.769032</v>
+        <v>12.639414</v>
       </c>
       <c r="O78">
-        <v>1.9153548</v>
+        <v>1.8959121</v>
       </c>
       <c r="P78">
-        <v>10.8536772</v>
+        <v>10.7435019</v>
       </c>
       <c r="Q78">
-        <v>10.8586772</v>
+        <v>10.7485019</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1716178913879721</v>
+        <v>0.1768659632144407</v>
       </c>
       <c r="T78">
-        <v>1.63982890428652</v>
+        <v>1.708228873304262</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.296221041424558</v>
+        <v>2.266399988938525</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09029027153932136</v>
+        <v>0.0904254491455294</v>
       </c>
       <c r="C79">
-        <v>27.89284169867105</v>
+        <v>25.95168364705111</v>
       </c>
       <c r="D79">
-        <v>152.3028416986711</v>
+        <v>152.0716836470511</v>
       </c>
       <c r="E79">
-        <v>94.47000000000001</v>
+        <v>96.17999999999999</v>
       </c>
       <c r="F79">
-        <v>131.67</v>
+        <v>133.38</v>
       </c>
       <c r="G79">
         <v>7.26</v>
@@ -7759,28 +7759,28 @@
         <v>22.62</v>
       </c>
       <c r="M79">
-        <v>9.980586000000002</v>
+        <v>10.110204</v>
       </c>
       <c r="N79">
-        <v>12.639414</v>
+        <v>12.509796</v>
       </c>
       <c r="O79">
-        <v>1.8959121</v>
+        <v>1.8764694</v>
       </c>
       <c r="P79">
-        <v>10.7435019</v>
+        <v>10.6333266</v>
       </c>
       <c r="Q79">
-        <v>10.7485019</v>
+        <v>10.6383266</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1768659632144407</v>
+        <v>0.1825911324796791</v>
       </c>
       <c r="T79">
-        <v>1.708228873304262</v>
+        <v>1.782847021323617</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.266399988938525</v>
+        <v>2.237343578823928</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0904254491455294</v>
+        <v>0.09056062675173746</v>
       </c>
       <c r="C80">
-        <v>25.95168364705111</v>
+        <v>24.01122621358729</v>
       </c>
       <c r="D80">
-        <v>152.0716836470511</v>
+        <v>151.8412262135873</v>
       </c>
       <c r="E80">
-        <v>96.17999999999999</v>
+        <v>97.89</v>
       </c>
       <c r="F80">
-        <v>133.38</v>
+        <v>135.09</v>
       </c>
       <c r="G80">
         <v>7.26</v>
@@ -7841,28 +7841,28 @@
         <v>22.62</v>
       </c>
       <c r="M80">
-        <v>10.110204</v>
+        <v>10.239822</v>
       </c>
       <c r="N80">
-        <v>12.509796</v>
+        <v>12.380178</v>
       </c>
       <c r="O80">
-        <v>1.8764694</v>
+        <v>1.8570267</v>
       </c>
       <c r="P80">
-        <v>10.6333266</v>
+        <v>10.5231513</v>
       </c>
       <c r="Q80">
-        <v>10.6383266</v>
+        <v>10.5281513</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1825911324796791</v>
+        <v>0.1888615559606545</v>
       </c>
       <c r="T80">
-        <v>1.782847021323617</v>
+        <v>1.864571659630529</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.237343578823928</v>
+        <v>2.209022774028689</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09056062675173746</v>
+        <v>0.0906958043579455</v>
       </c>
       <c r="C81">
-        <v>24.01122621358729</v>
+        <v>22.07146621783858</v>
       </c>
       <c r="D81">
-        <v>151.8412262135873</v>
+        <v>151.6114662178386</v>
       </c>
       <c r="E81">
-        <v>97.89</v>
+        <v>99.60000000000001</v>
       </c>
       <c r="F81">
-        <v>135.09</v>
+        <v>136.8</v>
       </c>
       <c r="G81">
         <v>7.26</v>
@@ -7923,28 +7923,28 @@
         <v>22.62</v>
       </c>
       <c r="M81">
-        <v>10.239822</v>
+        <v>10.36944</v>
       </c>
       <c r="N81">
-        <v>12.380178</v>
+        <v>12.25056</v>
       </c>
       <c r="O81">
-        <v>1.8570267</v>
+        <v>1.837584</v>
       </c>
       <c r="P81">
-        <v>10.5231513</v>
+        <v>10.412976</v>
       </c>
       <c r="Q81">
-        <v>10.5281513</v>
+        <v>10.417976</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1888615559606545</v>
+        <v>0.1957590217897275</v>
       </c>
       <c r="T81">
-        <v>1.864571659630529</v>
+        <v>1.954468761768133</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.209022774028689</v>
+        <v>2.18140998935333</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.0906958043579455</v>
+        <v>0.09083098196415354</v>
       </c>
       <c r="C82">
-        <v>22.07146621783858</v>
+        <v>20.13240049858484</v>
       </c>
       <c r="D82">
-        <v>151.6114662178386</v>
+        <v>151.3824004985849</v>
       </c>
       <c r="E82">
-        <v>99.60000000000001</v>
+        <v>101.31</v>
       </c>
       <c r="F82">
-        <v>136.8</v>
+        <v>138.51</v>
       </c>
       <c r="G82">
         <v>7.26</v>
@@ -8005,28 +8005,28 @@
         <v>22.62</v>
       </c>
       <c r="M82">
-        <v>10.36944</v>
+        <v>10.499058</v>
       </c>
       <c r="N82">
-        <v>12.25056</v>
+        <v>12.120942</v>
       </c>
       <c r="O82">
-        <v>1.837584</v>
+        <v>1.8181413</v>
       </c>
       <c r="P82">
-        <v>10.412976</v>
+        <v>10.3028007</v>
       </c>
       <c r="Q82">
-        <v>10.417976</v>
+        <v>10.3078007</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1957590217897275</v>
+        <v>0.2033825366534397</v>
       </c>
       <c r="T82">
-        <v>1.954468761768133</v>
+        <v>2.053828716762327</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.18140998935333</v>
+        <v>2.15447900183045</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09083098196415354</v>
+        <v>0.09096615957036158</v>
       </c>
       <c r="C83">
-        <v>20.13240049858484</v>
+        <v>18.194025913682</v>
       </c>
       <c r="D83">
-        <v>151.3824004985849</v>
+        <v>151.154025913682</v>
       </c>
       <c r="E83">
-        <v>101.31</v>
+        <v>103.02</v>
       </c>
       <c r="F83">
-        <v>138.51</v>
+        <v>140.22</v>
       </c>
       <c r="G83">
         <v>7.26</v>
@@ -8087,28 +8087,28 @@
         <v>22.62</v>
       </c>
       <c r="M83">
-        <v>10.499058</v>
+        <v>10.628676</v>
       </c>
       <c r="N83">
-        <v>12.120942</v>
+        <v>11.991324</v>
       </c>
       <c r="O83">
-        <v>1.8181413</v>
+        <v>1.7986986</v>
       </c>
       <c r="P83">
-        <v>10.3028007</v>
+        <v>10.1926254</v>
       </c>
       <c r="Q83">
-        <v>10.3078007</v>
+        <v>10.1976254</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2033825366534397</v>
+        <v>0.2118531087242311</v>
       </c>
       <c r="T83">
-        <v>2.053828716762327</v>
+        <v>2.164228666755875</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.15447900183045</v>
+        <v>2.128204867661786</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09096615957036158</v>
+        <v>0.09110133717656964</v>
       </c>
       <c r="C84">
-        <v>18.194025913682</v>
+        <v>16.25633933991816</v>
       </c>
       <c r="D84">
-        <v>151.154025913682</v>
+        <v>150.9263393399182</v>
       </c>
       <c r="E84">
-        <v>103.02</v>
+        <v>104.73</v>
       </c>
       <c r="F84">
-        <v>140.22</v>
+        <v>141.93</v>
       </c>
       <c r="G84">
         <v>7.26</v>
@@ -8169,28 +8169,28 @@
         <v>22.62</v>
       </c>
       <c r="M84">
-        <v>10.628676</v>
+        <v>10.758294</v>
       </c>
       <c r="N84">
-        <v>11.991324</v>
+        <v>11.861706</v>
       </c>
       <c r="O84">
-        <v>1.7986986</v>
+        <v>1.7792559</v>
       </c>
       <c r="P84">
-        <v>10.1926254</v>
+        <v>10.0824501</v>
       </c>
       <c r="Q84">
-        <v>10.1976254</v>
+        <v>10.0874501</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2118531087242311</v>
+        <v>0.2213202186857038</v>
       </c>
       <c r="T84">
-        <v>2.164228666755875</v>
+        <v>2.287616846160429</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.128204867661786</v>
+        <v>2.102563845159836</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09110133717656964</v>
+        <v>0.09123651478277769</v>
       </c>
       <c r="C85">
-        <v>16.25633933991816</v>
+        <v>14.31933767287151</v>
       </c>
       <c r="D85">
-        <v>150.9263393399182</v>
+        <v>150.6993376728715</v>
       </c>
       <c r="E85">
-        <v>104.73</v>
+        <v>106.44</v>
       </c>
       <c r="F85">
-        <v>141.93</v>
+        <v>143.64</v>
       </c>
       <c r="G85">
         <v>7.26</v>
@@ -8251,28 +8251,28 @@
         <v>22.62</v>
       </c>
       <c r="M85">
-        <v>10.758294</v>
+        <v>10.887912</v>
       </c>
       <c r="N85">
-        <v>11.861706</v>
+        <v>11.732088</v>
       </c>
       <c r="O85">
-        <v>1.7792559</v>
+        <v>1.7598132</v>
       </c>
       <c r="P85">
-        <v>10.0824501</v>
+        <v>9.972274799999999</v>
       </c>
       <c r="Q85">
-        <v>10.0874501</v>
+        <v>9.9772748</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2213202186857038</v>
+        <v>0.2319707173923606</v>
       </c>
       <c r="T85">
-        <v>2.287616846160429</v>
+        <v>2.426428547990552</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.102563845159836</v>
+        <v>2.077533323193648</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09123651478277769</v>
+        <v>0.09137169238898574</v>
       </c>
       <c r="C86">
-        <v>14.31933767287154</v>
+        <v>12.38301782676913</v>
       </c>
       <c r="D86">
-        <v>150.6993376728715</v>
+        <v>150.4730178267691</v>
       </c>
       <c r="E86">
-        <v>106.44</v>
+        <v>108.15</v>
       </c>
       <c r="F86">
-        <v>143.64</v>
+        <v>145.35</v>
       </c>
       <c r="G86">
         <v>7.26</v>
@@ -8333,28 +8333,28 @@
         <v>22.62</v>
       </c>
       <c r="M86">
-        <v>10.887912</v>
+        <v>11.01753</v>
       </c>
       <c r="N86">
-        <v>11.732088</v>
+        <v>11.60247</v>
       </c>
       <c r="O86">
-        <v>1.7598132</v>
+        <v>1.7403705</v>
       </c>
       <c r="P86">
-        <v>9.972274800000001</v>
+        <v>9.862099499999999</v>
       </c>
       <c r="Q86">
-        <v>9.977274800000002</v>
+        <v>9.8670995</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2319707173923605</v>
+        <v>0.2440412825932382</v>
       </c>
       <c r="T86">
-        <v>2.426428547990551</v>
+        <v>2.583748476731357</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.077533323193648</v>
+        <v>2.053091754685488</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09137169238898574</v>
+        <v>0.09150686999519378</v>
       </c>
       <c r="C87">
-        <v>12.38301782676913</v>
+        <v>10.44737673434693</v>
       </c>
       <c r="D87">
-        <v>150.4730178267691</v>
+        <v>150.2473767343469</v>
       </c>
       <c r="E87">
-        <v>108.15</v>
+        <v>109.86</v>
       </c>
       <c r="F87">
-        <v>145.35</v>
+        <v>147.06</v>
       </c>
       <c r="G87">
         <v>7.26</v>
@@ -8415,28 +8415,28 @@
         <v>22.62</v>
       </c>
       <c r="M87">
-        <v>11.01753</v>
+        <v>11.147148</v>
       </c>
       <c r="N87">
-        <v>11.60247</v>
+        <v>11.472852</v>
       </c>
       <c r="O87">
-        <v>1.7403705</v>
+        <v>1.7209278</v>
       </c>
       <c r="P87">
-        <v>9.862099499999999</v>
+        <v>9.751924199999999</v>
       </c>
       <c r="Q87">
-        <v>9.8670995</v>
+        <v>9.7569242</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2440412825932382</v>
+        <v>0.2578362142513841</v>
       </c>
       <c r="T87">
-        <v>2.583748476731357</v>
+        <v>2.763542681006564</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.053091754685488</v>
+        <v>2.029218594747284</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09150686999519378</v>
+        <v>0.09164204760140182</v>
       </c>
       <c r="C88">
-        <v>10.44737673434693</v>
+        <v>8.512411346711417</v>
       </c>
       <c r="D88">
-        <v>150.2473767343469</v>
+        <v>150.0224113467114</v>
       </c>
       <c r="E88">
-        <v>109.86</v>
+        <v>111.57</v>
       </c>
       <c r="F88">
-        <v>147.06</v>
+        <v>148.77</v>
       </c>
       <c r="G88">
         <v>7.26</v>
@@ -8497,28 +8497,28 @@
         <v>22.62</v>
       </c>
       <c r="M88">
-        <v>11.147148</v>
+        <v>11.276766</v>
       </c>
       <c r="N88">
-        <v>11.472852</v>
+        <v>11.343234</v>
       </c>
       <c r="O88">
-        <v>1.7209278</v>
+        <v>1.7014851</v>
       </c>
       <c r="P88">
-        <v>9.751924199999999</v>
+        <v>9.6417489</v>
       </c>
       <c r="Q88">
-        <v>9.7569242</v>
+        <v>9.6467489</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2578362142513841</v>
+        <v>0.2737534430877063</v>
       </c>
       <c r="T88">
-        <v>2.763542681006564</v>
+        <v>2.970997532093341</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.029218594747284</v>
+        <v>2.005894243083522</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09164204760140182</v>
+        <v>0.1023988252076099</v>
       </c>
       <c r="C89">
-        <v>8.512411346711417</v>
+        <v>-9.169427433501539</v>
       </c>
       <c r="D89">
-        <v>150.0224113467114</v>
+        <v>134.0505725664985</v>
       </c>
       <c r="E89">
-        <v>111.57</v>
+        <v>113.28</v>
       </c>
       <c r="F89">
-        <v>148.77</v>
+        <v>150.48</v>
       </c>
       <c r="G89">
         <v>7.26</v>
@@ -8579,45 +8579,45 @@
         <v>22.62</v>
       </c>
       <c r="M89">
-        <v>11.276766</v>
+        <v>13.5432</v>
       </c>
       <c r="N89">
-        <v>11.343234</v>
+        <v>9.076800000000002</v>
       </c>
       <c r="O89">
-        <v>1.7014851</v>
+        <v>1.36152</v>
       </c>
       <c r="P89">
-        <v>9.6417489</v>
+        <v>7.715280000000002</v>
       </c>
       <c r="Q89">
-        <v>9.6467489</v>
+        <v>7.720280000000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2737534430877063</v>
+        <v>0.2923235433967489</v>
       </c>
       <c r="T89">
-        <v>2.970997532093341</v>
+        <v>3.213028191694582</v>
       </c>
       <c r="U89">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V89">
         <v>0.15</v>
       </c>
       <c r="W89">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y89">
-        <v>2.005894243083522</v>
+        <v>1.670210880737197</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1023988252076099</v>
+        <v>0.1026547028138179</v>
       </c>
       <c r="C90">
-        <v>-9.169427433501539</v>
+        <v>-11.21805248165077</v>
       </c>
       <c r="D90">
-        <v>134.0505725664985</v>
+        <v>133.7119475183492</v>
       </c>
       <c r="E90">
-        <v>113.28</v>
+        <v>114.99</v>
       </c>
       <c r="F90">
-        <v>150.48</v>
+        <v>152.19</v>
       </c>
       <c r="G90">
         <v>7.26</v>
@@ -8661,28 +8661,28 @@
         <v>22.62</v>
       </c>
       <c r="M90">
-        <v>13.5432</v>
+        <v>13.6971</v>
       </c>
       <c r="N90">
-        <v>9.076800000000002</v>
+        <v>8.922900000000002</v>
       </c>
       <c r="O90">
-        <v>1.36152</v>
+        <v>1.338435</v>
       </c>
       <c r="P90">
-        <v>7.715280000000002</v>
+        <v>7.584465000000002</v>
       </c>
       <c r="Q90">
-        <v>7.720280000000002</v>
+        <v>7.589465000000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2923235433967489</v>
+        <v>0.3142700255801629</v>
       </c>
       <c r="T90">
-        <v>3.213028191694582</v>
+        <v>3.499064425768775</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.670210880737197</v>
+        <v>1.651444466346891</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1026547028138179</v>
+        <v>0.102910580420026</v>
       </c>
       <c r="C91">
-        <v>-11.21805248165077</v>
+        <v>-13.26497103961671</v>
       </c>
       <c r="D91">
-        <v>133.7119475183492</v>
+        <v>133.3750289603833</v>
       </c>
       <c r="E91">
-        <v>114.99</v>
+        <v>116.7</v>
       </c>
       <c r="F91">
-        <v>152.19</v>
+        <v>153.9</v>
       </c>
       <c r="G91">
         <v>7.26</v>
@@ -8743,28 +8743,28 @@
         <v>22.62</v>
       </c>
       <c r="M91">
-        <v>13.6971</v>
+        <v>13.851</v>
       </c>
       <c r="N91">
-        <v>8.922900000000002</v>
+        <v>8.769</v>
       </c>
       <c r="O91">
-        <v>1.338435</v>
+        <v>1.31535</v>
       </c>
       <c r="P91">
-        <v>7.584465000000002</v>
+        <v>7.45365</v>
       </c>
       <c r="Q91">
-        <v>7.589465000000001</v>
+        <v>7.45865</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3142700255801629</v>
+        <v>0.3406058042002598</v>
       </c>
       <c r="T91">
-        <v>3.499064425768775</v>
+        <v>3.842307906657807</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.651444466346891</v>
+        <v>1.633095083387481</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.102910580420026</v>
+        <v>0.103166458026234</v>
       </c>
       <c r="C92">
-        <v>-13.26497103961671</v>
+        <v>-15.3101959746819</v>
       </c>
       <c r="D92">
-        <v>133.3750289603833</v>
+        <v>133.0398040253181</v>
       </c>
       <c r="E92">
-        <v>116.7</v>
+        <v>118.41</v>
       </c>
       <c r="F92">
-        <v>153.9</v>
+        <v>155.61</v>
       </c>
       <c r="G92">
         <v>7.26</v>
@@ -8825,28 +8825,28 @@
         <v>22.62</v>
       </c>
       <c r="M92">
-        <v>13.851</v>
+        <v>14.0049</v>
       </c>
       <c r="N92">
-        <v>8.769</v>
+        <v>8.6151</v>
       </c>
       <c r="O92">
-        <v>1.31535</v>
+        <v>1.292265</v>
       </c>
       <c r="P92">
-        <v>7.45365</v>
+        <v>7.322835</v>
       </c>
       <c r="Q92">
-        <v>7.45865</v>
+        <v>7.327834999999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3406058042002598</v>
+        <v>0.3727939780692669</v>
       </c>
       <c r="T92">
-        <v>3.842307906657807</v>
+        <v>4.26182771663329</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.633095083387481</v>
+        <v>1.615148983570036</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.103166458026234</v>
+        <v>0.1034223356324421</v>
       </c>
       <c r="C93">
-        <v>-15.3101959746819</v>
+        <v>-17.3537400250907</v>
       </c>
       <c r="D93">
-        <v>133.0398040253181</v>
+        <v>132.7062599749093</v>
       </c>
       <c r="E93">
-        <v>118.41</v>
+        <v>120.12</v>
       </c>
       <c r="F93">
-        <v>155.61</v>
+        <v>157.32</v>
       </c>
       <c r="G93">
         <v>7.26</v>
@@ -8907,28 +8907,28 @@
         <v>22.62</v>
       </c>
       <c r="M93">
-        <v>14.0049</v>
+        <v>14.1588</v>
       </c>
       <c r="N93">
-        <v>8.6151</v>
+        <v>8.461200000000002</v>
       </c>
       <c r="O93">
-        <v>1.292265</v>
+        <v>1.26918</v>
       </c>
       <c r="P93">
-        <v>7.322835</v>
+        <v>7.192020000000001</v>
       </c>
       <c r="Q93">
-        <v>7.327834999999999</v>
+        <v>7.197020000000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3727939780692669</v>
+        <v>0.413029195405526</v>
       </c>
       <c r="T93">
-        <v>4.26182771663329</v>
+        <v>4.786227479102645</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.615148983570036</v>
+        <v>1.597593016357318</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1034223356324421</v>
+        <v>0.1036782132386501</v>
       </c>
       <c r="C94">
-        <v>-17.3537400250907</v>
+        <v>-19.39561580166267</v>
       </c>
       <c r="D94">
-        <v>132.7062599749093</v>
+        <v>132.3743841983373</v>
       </c>
       <c r="E94">
-        <v>120.12</v>
+        <v>121.83</v>
       </c>
       <c r="F94">
-        <v>157.32</v>
+        <v>159.03</v>
       </c>
       <c r="G94">
         <v>7.26</v>
@@ -8989,28 +8989,28 @@
         <v>22.62</v>
       </c>
       <c r="M94">
-        <v>14.1588</v>
+        <v>14.3127</v>
       </c>
       <c r="N94">
-        <v>8.461200000000002</v>
+        <v>8.307300000000001</v>
       </c>
       <c r="O94">
-        <v>1.26918</v>
+        <v>1.246095</v>
       </c>
       <c r="P94">
-        <v>7.192020000000001</v>
+        <v>7.061205000000001</v>
       </c>
       <c r="Q94">
-        <v>7.197020000000001</v>
+        <v>7.066205000000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.413029195405526</v>
+        <v>0.4647601891235733</v>
       </c>
       <c r="T94">
-        <v>4.786227479102645</v>
+        <v>5.460455745134673</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.597593016357318</v>
+        <v>1.580414596826595</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1036782132386501</v>
+        <v>0.1039340908448581</v>
       </c>
       <c r="C95">
-        <v>-19.39561580166267</v>
+        <v>-21.435835789382</v>
       </c>
       <c r="D95">
-        <v>132.3743841983373</v>
+        <v>132.044164210618</v>
       </c>
       <c r="E95">
-        <v>121.83</v>
+        <v>123.54</v>
       </c>
       <c r="F95">
-        <v>159.03</v>
+        <v>160.74</v>
       </c>
       <c r="G95">
         <v>7.26</v>
@@ -9071,28 +9071,28 @@
         <v>22.62</v>
       </c>
       <c r="M95">
-        <v>14.3127</v>
+        <v>14.4666</v>
       </c>
       <c r="N95">
-        <v>8.307300000000001</v>
+        <v>8.153400000000001</v>
       </c>
       <c r="O95">
-        <v>1.246095</v>
+        <v>1.22301</v>
       </c>
       <c r="P95">
-        <v>7.061205000000001</v>
+        <v>6.930390000000001</v>
       </c>
       <c r="Q95">
-        <v>7.066205000000001</v>
+        <v>6.935390000000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4647601891235733</v>
+        <v>0.533734847414303</v>
       </c>
       <c r="T95">
-        <v>5.460455745134673</v>
+        <v>6.359426766510709</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.580414596826595</v>
+        <v>1.563601675583759</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1039340908448581</v>
+        <v>0.1041899684510662</v>
       </c>
       <c r="C96">
-        <v>-21.435835789382</v>
+        <v>-23.47441234896323</v>
       </c>
       <c r="D96">
-        <v>132.044164210618</v>
+        <v>131.7155876510368</v>
       </c>
       <c r="E96">
-        <v>123.54</v>
+        <v>125.25</v>
       </c>
       <c r="F96">
-        <v>160.74</v>
+        <v>162.45</v>
       </c>
       <c r="G96">
         <v>7.26</v>
@@ -9153,28 +9153,28 @@
         <v>22.62</v>
       </c>
       <c r="M96">
-        <v>14.4666</v>
+        <v>14.6205</v>
       </c>
       <c r="N96">
-        <v>8.153400000000001</v>
+        <v>7.999499999999999</v>
       </c>
       <c r="O96">
-        <v>1.22301</v>
+        <v>1.199925</v>
       </c>
       <c r="P96">
-        <v>6.930390000000001</v>
+        <v>6.799574999999999</v>
       </c>
       <c r="Q96">
-        <v>6.935390000000001</v>
+        <v>6.804574999999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.533734847414303</v>
+        <v>0.6302993690213249</v>
       </c>
       <c r="T96">
-        <v>6.359426766510709</v>
+        <v>7.617986196437164</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.563601675583759</v>
+        <v>1.547142710577614</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1041899684510662</v>
+        <v>0.1044458460572742</v>
       </c>
       <c r="C97">
-        <v>-23.47441234896323</v>
+        <v>-25.51135771839338</v>
       </c>
       <c r="D97">
-        <v>131.7155876510368</v>
+        <v>131.3886422816066</v>
       </c>
       <c r="E97">
-        <v>125.25</v>
+        <v>126.96</v>
       </c>
       <c r="F97">
-        <v>162.45</v>
+        <v>164.16</v>
       </c>
       <c r="G97">
         <v>7.26</v>
@@ -9235,28 +9235,28 @@
         <v>22.62</v>
       </c>
       <c r="M97">
-        <v>14.6205</v>
+        <v>14.7744</v>
       </c>
       <c r="N97">
-        <v>7.999499999999999</v>
+        <v>7.845599999999999</v>
       </c>
       <c r="O97">
-        <v>1.199925</v>
+        <v>1.17684</v>
       </c>
       <c r="P97">
-        <v>6.799574999999999</v>
+        <v>6.668759999999999</v>
       </c>
       <c r="Q97">
-        <v>6.804574999999999</v>
+        <v>6.673759999999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6302993690213249</v>
+        <v>0.7751461514318576</v>
       </c>
       <c r="T97">
-        <v>7.617986196437164</v>
+        <v>9.505825341326844</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.547142710577614</v>
+        <v>1.531026640675763</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1044458460572742</v>
+        <v>0.1047017236634823</v>
       </c>
       <c r="C98">
-        <v>-25.51135771839333</v>
+        <v>-27.54668401445153</v>
       </c>
       <c r="D98">
-        <v>131.3886422816067</v>
+        <v>131.0633159855485</v>
       </c>
       <c r="E98">
-        <v>126.96</v>
+        <v>128.67</v>
       </c>
       <c r="F98">
-        <v>164.16</v>
+        <v>165.87</v>
       </c>
       <c r="G98">
         <v>7.26</v>
@@ -9317,28 +9317,28 @@
         <v>22.62</v>
       </c>
       <c r="M98">
-        <v>14.7744</v>
+        <v>14.9283</v>
       </c>
       <c r="N98">
-        <v>7.845600000000001</v>
+        <v>7.691700000000001</v>
       </c>
       <c r="O98">
-        <v>1.17684</v>
+        <v>1.153755</v>
       </c>
       <c r="P98">
-        <v>6.668760000000001</v>
+        <v>6.537945000000001</v>
       </c>
       <c r="Q98">
-        <v>6.673760000000001</v>
+        <v>6.542945</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7751461514318555</v>
+        <v>1.016557455449409</v>
       </c>
       <c r="T98">
-        <v>9.505825341326817</v>
+        <v>12.65222391614294</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.531026640675764</v>
+        <v>1.515242860874983</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1047017236634823</v>
+        <v>0.1544128787955801</v>
       </c>
       <c r="C99">
-        <v>-27.54668401445153</v>
+        <v>-71.82600487708903</v>
       </c>
       <c r="D99">
-        <v>131.0633159855485</v>
+        <v>88.49399512291095</v>
       </c>
       <c r="E99">
-        <v>128.67</v>
+        <v>130.38</v>
       </c>
       <c r="F99">
-        <v>165.87</v>
+        <v>167.58</v>
       </c>
       <c r="G99">
         <v>7.26</v>
@@ -9399,45 +9399,45 @@
         <v>22.62</v>
       </c>
       <c r="M99">
-        <v>14.9283</v>
+        <v>24.600744</v>
       </c>
       <c r="N99">
-        <v>7.691700000000001</v>
+        <v>-1.980743999999998</v>
       </c>
       <c r="O99">
-        <v>1.153755</v>
+        <v>-0.2971115999999996</v>
       </c>
       <c r="P99">
-        <v>6.537945000000001</v>
+        <v>-1.683632399999998</v>
       </c>
       <c r="Q99">
-        <v>6.542945</v>
+        <v>-1.678632399999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.016557455449409</v>
+        <v>1.519549202936897</v>
       </c>
       <c r="T99">
-        <v>12.65222391614294</v>
+        <v>19.20789256587538</v>
       </c>
       <c r="U99">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.15</v>
+        <v>0.1379226579488816</v>
       </c>
       <c r="W99">
-        <v>0.0765</v>
+        <v>0.1265529538131042</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>1.515242860874983</v>
+        <v>0.919484386325877</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1544128787955801</v>
+        <v>0.1554228787955801</v>
       </c>
       <c r="C100">
-        <v>-71.82600487708903</v>
+        <v>-74.11615496683854</v>
       </c>
       <c r="D100">
-        <v>88.49399512291095</v>
+        <v>87.91384503316145</v>
       </c>
       <c r="E100">
-        <v>130.38</v>
+        <v>132.09</v>
       </c>
       <c r="F100">
-        <v>167.58</v>
+        <v>169.29</v>
       </c>
       <c r="G100">
         <v>7.26</v>
@@ -9481,37 +9481,37 @@
         <v>22.62</v>
       </c>
       <c r="M100">
-        <v>24.600744</v>
+        <v>24.851772</v>
       </c>
       <c r="N100">
-        <v>-1.980743999999998</v>
+        <v>-2.231771999999999</v>
       </c>
       <c r="O100">
-        <v>-0.2971115999999996</v>
+        <v>-0.3347657999999999</v>
       </c>
       <c r="P100">
-        <v>-1.683632399999998</v>
+        <v>-1.897006199999999</v>
       </c>
       <c r="Q100">
-        <v>-1.678632399999998</v>
+        <v>-1.8920062</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.519549202936897</v>
+        <v>2.993298405873794</v>
       </c>
       <c r="T100">
-        <v>19.20789256587538</v>
+        <v>38.41578513175075</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1379226579488816</v>
+        <v>0.1365294997877817</v>
       </c>
       <c r="W100">
-        <v>0.1265529538131042</v>
+        <v>0.1267574694311537</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.919484386325877</v>
+        <v>0.9101966652518783</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1554228787955801</v>
-      </c>
-      <c r="C101">
-        <v>-74.11615496683854</v>
-      </c>
-      <c r="D101">
-        <v>87.91384503316145</v>
-      </c>
-      <c r="E101">
-        <v>132.09</v>
-      </c>
-      <c r="F101">
-        <v>169.29</v>
-      </c>
-      <c r="G101">
-        <v>7.26</v>
-      </c>
-      <c r="H101">
-        <v>133.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>22.625</v>
-      </c>
-      <c r="K101">
-        <v>0.005</v>
-      </c>
-      <c r="L101">
-        <v>22.62</v>
-      </c>
-      <c r="M101">
-        <v>24.851772</v>
-      </c>
-      <c r="N101">
-        <v>-2.231771999999999</v>
-      </c>
-      <c r="O101">
-        <v>-0.3347657999999999</v>
-      </c>
-      <c r="P101">
-        <v>-1.897006199999999</v>
-      </c>
-      <c r="Q101">
-        <v>-1.8920062</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.993298405873794</v>
-      </c>
-      <c r="T101">
-        <v>38.41578513175075</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1365294997877817</v>
-      </c>
-      <c r="W101">
-        <v>0.1267574694311537</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.9101966652518783</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
